--- a/data/Employee_Expenses.xlsx
+++ b/data/Employee_Expenses.xlsx
@@ -5,22 +5,25 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aneeba.hamid_karanda\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aneeba.hamid_karanda\Downloads\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947030A2-1439-459D-93E3-2CEA47909431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B04E037-0483-4D8A-B79C-639A1A7CDE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E91F72FA-45AE-41E4-B25B-09DB7C520744}"/>
   </bookViews>
   <sheets>
     <sheet name="Employee Expenses (76)" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Employee Expenses (76)'!$A$1:$J$409</definedName>
+  </definedNames>
   <calcPr calcId="191029" iterate="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2890" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2862" uniqueCount="381">
   <si>
     <t>Employee Name</t>
   </si>
@@ -578,9 +581,6 @@
   </si>
   <si>
     <t>International Trip- Gates Foundation Workshop UK Sept 2026</t>
-  </si>
-  <si>
-    <t>Communication reimbursement CFO</t>
   </si>
   <si>
     <t>11-701-FIN1-H106003-401-ISB-11-211-000-0000-00</t>
@@ -2008,11 +2008,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AE04198-225E-4952-AFA7-99BB4D284234}">
-  <dimension ref="A1:J413"/>
+  <dimension ref="A1:J409"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.1796875" customWidth="1"/>
     <col min="4" max="4" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2050,7 +2051,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -2082,7 +2083,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
@@ -2114,7 +2115,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -2146,7 +2147,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -2178,7 +2179,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -2210,7 +2211,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -2242,7 +2243,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -2274,7 +2275,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -2306,7 +2307,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -2338,7 +2339,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
@@ -2370,7 +2371,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -2399,7 +2400,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -2428,7 +2429,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
@@ -2457,7 +2458,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
@@ -2489,7 +2490,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -2521,7 +2522,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
@@ -2553,7 +2554,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B18" t="s">
         <v>35</v>
@@ -2585,7 +2586,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
@@ -2614,7 +2615,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
@@ -2643,7 +2644,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B21" t="s">
         <v>41</v>
@@ -2672,7 +2673,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B22" t="s">
         <v>41</v>
@@ -2701,7 +2702,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -2733,7 +2734,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
@@ -2765,7 +2766,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -2797,7 +2798,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
@@ -2829,7 +2830,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B27" t="s">
         <v>29</v>
@@ -2861,7 +2862,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B28" t="s">
         <v>24</v>
@@ -2893,7 +2894,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B29" t="s">
         <v>24</v>
@@ -2925,7 +2926,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B30" t="s">
         <v>24</v>
@@ -2954,7 +2955,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B31" t="s">
         <v>24</v>
@@ -2983,7 +2984,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B32" t="s">
         <v>43</v>
@@ -3015,7 +3016,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
@@ -3047,7 +3048,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s">
         <v>45</v>
@@ -3079,7 +3080,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s">
         <v>45</v>
@@ -3111,7 +3112,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B36" t="s">
         <v>46</v>
@@ -3143,7 +3144,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B37" t="s">
         <v>51</v>
@@ -3175,7 +3176,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s">
         <v>51</v>
@@ -3207,7 +3208,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B39" t="s">
         <v>56</v>
@@ -3239,7 +3240,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s">
         <v>58</v>
@@ -3271,7 +3272,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s">
         <v>58</v>
@@ -3303,7 +3304,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B42" t="s">
         <v>59</v>
@@ -3332,7 +3333,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B43" t="s">
         <v>59</v>
@@ -3361,7 +3362,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B44" t="s">
         <v>60</v>
@@ -3393,7 +3394,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B45" t="s">
         <v>60</v>
@@ -3425,7 +3426,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B46" t="s">
         <v>63</v>
@@ -3457,7 +3458,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B47" t="s">
         <v>63</v>
@@ -3489,7 +3490,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B48" t="s">
         <v>66</v>
@@ -3521,7 +3522,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B49" t="s">
         <v>66</v>
@@ -3553,7 +3554,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B50" t="s">
         <v>67</v>
@@ -3585,7 +3586,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B51" t="s">
         <v>67</v>
@@ -3617,7 +3618,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B52" t="s">
         <v>68</v>
@@ -3649,7 +3650,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B53" t="s">
         <v>68</v>
@@ -3681,7 +3682,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B54" t="s">
         <v>73</v>
@@ -3710,7 +3711,7 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B55" t="s">
         <v>73</v>
@@ -3739,7 +3740,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B56" t="s">
         <v>75</v>
@@ -3768,7 +3769,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B57" t="s">
         <v>75</v>
@@ -3797,7 +3798,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B58" t="s">
         <v>78</v>
@@ -3829,7 +3830,7 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B59" t="s">
         <v>78</v>
@@ -3861,7 +3862,7 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B60" t="s">
         <v>78</v>
@@ -3893,7 +3894,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B61" t="s">
         <v>78</v>
@@ -3925,7 +3926,7 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B62" t="s">
         <v>81</v>
@@ -3957,7 +3958,7 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B63" t="s">
         <v>81</v>
@@ -3989,7 +3990,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B64" t="s">
         <v>81</v>
@@ -4021,7 +4022,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B65" t="s">
         <v>81</v>
@@ -4053,7 +4054,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B66" t="s">
         <v>82</v>
@@ -4085,7 +4086,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B67" t="s">
         <v>82</v>
@@ -4117,7 +4118,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B68" t="s">
         <v>82</v>
@@ -4149,7 +4150,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B69" t="s">
         <v>82</v>
@@ -4181,7 +4182,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B70" t="s">
         <v>83</v>
@@ -4210,7 +4211,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B71" t="s">
         <v>83</v>
@@ -4239,7 +4240,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B72" t="s">
         <v>83</v>
@@ -4268,7 +4269,7 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B73" t="s">
         <v>83</v>
@@ -4297,7 +4298,7 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B74" t="s">
         <v>84</v>
@@ -4326,7 +4327,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B75" t="s">
         <v>84</v>
@@ -4355,7 +4356,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B76" t="s">
         <v>84</v>
@@ -4384,7 +4385,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B77" t="s">
         <v>84</v>
@@ -4413,7 +4414,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B78" t="s">
         <v>85</v>
@@ -4445,7 +4446,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B79" t="s">
         <v>89</v>
@@ -4477,7 +4478,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B80" t="s">
         <v>89</v>
@@ -4509,7 +4510,7 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B81" t="s">
         <v>94</v>
@@ -4541,7 +4542,7 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B82" t="s">
         <v>94</v>
@@ -4573,7 +4574,7 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B83" t="s">
         <v>97</v>
@@ -4605,7 +4606,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B84" t="s">
         <v>97</v>
@@ -4637,7 +4638,7 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B85" t="s">
         <v>98</v>
@@ -4669,7 +4670,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B86" t="s">
         <v>98</v>
@@ -4701,7 +4702,7 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B87" t="s">
         <v>99</v>
@@ -4730,7 +4731,7 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B88" t="s">
         <v>99</v>
@@ -4759,7 +4760,7 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B89" t="s">
         <v>99</v>
@@ -4788,7 +4789,7 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B90" t="s">
         <v>99</v>
@@ -4817,7 +4818,7 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B91" t="s">
         <v>105</v>
@@ -4846,7 +4847,7 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B92" t="s">
         <v>107</v>
@@ -4875,7 +4876,7 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B93" t="s">
         <v>107</v>
@@ -4904,7 +4905,7 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B94" t="s">
         <v>107</v>
@@ -4933,7 +4934,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B95" t="s">
         <v>107</v>
@@ -4962,7 +4963,7 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B96" t="s">
         <v>27</v>
@@ -4994,7 +4995,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B97" t="s">
         <v>27</v>
@@ -5026,7 +5027,7 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B98" t="s">
         <v>112</v>
@@ -5058,7 +5059,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B99" t="s">
         <v>114</v>
@@ -5090,7 +5091,7 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B100" t="s">
         <v>116</v>
@@ -5122,7 +5123,7 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B101" t="s">
         <v>29</v>
@@ -5154,7 +5155,7 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B102" t="s">
         <v>119</v>
@@ -5183,7 +5184,7 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B103" t="s">
         <v>121</v>
@@ -5212,7 +5213,7 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B104" t="s">
         <v>121</v>
@@ -5241,7 +5242,7 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B105" t="s">
         <v>60</v>
@@ -5273,7 +5274,7 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B106" t="s">
         <v>60</v>
@@ -5305,7 +5306,7 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B107" t="s">
         <v>122</v>
@@ -5337,7 +5338,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B108" t="s">
         <v>122</v>
@@ -5369,7 +5370,7 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B109" t="s">
         <v>123</v>
@@ -5398,7 +5399,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B110" t="s">
         <v>123</v>
@@ -5427,7 +5428,7 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B111" t="s">
         <v>24</v>
@@ -5459,7 +5460,7 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B112" t="s">
         <v>24</v>
@@ -5491,7 +5492,7 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B113" t="s">
         <v>24</v>
@@ -5523,7 +5524,7 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B114" t="s">
         <v>24</v>
@@ -5555,7 +5556,7 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B115" t="s">
         <v>24</v>
@@ -5587,7 +5588,7 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B116" t="s">
         <v>24</v>
@@ -5619,7 +5620,7 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B117" t="s">
         <v>126</v>
@@ -5648,7 +5649,7 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B118" t="s">
         <v>126</v>
@@ -5677,7 +5678,7 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B119" t="s">
         <v>127</v>
@@ -5706,7 +5707,7 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B120" t="s">
         <v>127</v>
@@ -5735,7 +5736,7 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B121" t="s">
         <v>132</v>
@@ -5764,7 +5765,7 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B122" t="s">
         <v>132</v>
@@ -5793,7 +5794,7 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B123" t="s">
         <v>24</v>
@@ -5825,7 +5826,7 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B124" t="s">
         <v>24</v>
@@ -5857,7 +5858,7 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B125" t="s">
         <v>24</v>
@@ -5889,7 +5890,7 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B126" t="s">
         <v>135</v>
@@ -5918,7 +5919,7 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B127" t="s">
         <v>136</v>
@@ -5950,7 +5951,7 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B128" t="s">
         <v>123</v>
@@ -5982,7 +5983,7 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B129" t="s">
         <v>137</v>
@@ -6014,7 +6015,7 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B130" t="s">
         <v>139</v>
@@ -6046,7 +6047,7 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B131" t="s">
         <v>141</v>
@@ -6078,7 +6079,7 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B132" t="s">
         <v>137</v>
@@ -6110,7 +6111,7 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B133" t="s">
         <v>142</v>
@@ -6142,7 +6143,7 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B134" t="s">
         <v>143</v>
@@ -6174,7 +6175,7 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B135" t="s">
         <v>137</v>
@@ -6203,7 +6204,7 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B136" t="s">
         <v>145</v>
@@ -6232,7 +6233,7 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B137" t="s">
         <v>146</v>
@@ -6264,7 +6265,7 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B138" t="s">
         <v>146</v>
@@ -6296,7 +6297,7 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B139" t="s">
         <v>146</v>
@@ -6328,7 +6329,7 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B140" t="s">
         <v>146</v>
@@ -6360,7 +6361,7 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B141" t="s">
         <v>24</v>
@@ -6392,7 +6393,7 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B142" t="s">
         <v>24</v>
@@ -6424,7 +6425,7 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B143" t="s">
         <v>149</v>
@@ -6456,7 +6457,7 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B144" t="s">
         <v>149</v>
@@ -6488,7 +6489,7 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B145" t="s">
         <v>150</v>
@@ -6520,7 +6521,7 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B146" t="s">
         <v>152</v>
@@ -6549,7 +6550,7 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B147" t="s">
         <v>152</v>
@@ -6578,7 +6579,7 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B148" t="s">
         <v>155</v>
@@ -6610,7 +6611,7 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B149" t="s">
         <v>155</v>
@@ -6642,7 +6643,7 @@
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B150" t="s">
         <v>24</v>
@@ -6674,7 +6675,7 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B151" t="s">
         <v>24</v>
@@ -6706,7 +6707,7 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B152" t="s">
         <v>158</v>
@@ -6738,7 +6739,7 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B153" t="s">
         <v>158</v>
@@ -6770,7 +6771,7 @@
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B154" t="s">
         <v>24</v>
@@ -6802,7 +6803,7 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B155" t="s">
         <v>24</v>
@@ -6834,7 +6835,7 @@
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B156" t="s">
         <v>24</v>
@@ -6866,7 +6867,7 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B157" t="s">
         <v>24</v>
@@ -6898,7 +6899,7 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B158" t="s">
         <v>24</v>
@@ -6930,7 +6931,7 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B159" t="s">
         <v>24</v>
@@ -6962,7 +6963,7 @@
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B160" t="s">
         <v>24</v>
@@ -6994,7 +6995,7 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B161" t="s">
         <v>24</v>
@@ -7026,7 +7027,7 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B162" t="s">
         <v>24</v>
@@ -7058,7 +7059,7 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B163" t="s">
         <v>24</v>
@@ -7090,7 +7091,7 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B164" t="s">
         <v>24</v>
@@ -7122,7 +7123,7 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B165" t="s">
         <v>24</v>
@@ -7154,7 +7155,7 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B166" t="s">
         <v>24</v>
@@ -7183,7 +7184,7 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B167" t="s">
         <v>24</v>
@@ -7212,7 +7213,7 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B168" t="s">
         <v>24</v>
@@ -7241,7 +7242,7 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B169" t="s">
         <v>24</v>
@@ -7270,7 +7271,7 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B170" t="s">
         <v>29</v>
@@ -7299,7 +7300,7 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B171" t="s">
         <v>163</v>
@@ -7331,7 +7332,7 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B172" t="s">
         <v>164</v>
@@ -7363,7 +7364,7 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B173" t="s">
         <v>165</v>
@@ -7392,7 +7393,7 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B174" t="s">
         <v>166</v>
@@ -7424,7 +7425,7 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B175" t="s">
         <v>167</v>
@@ -7456,7 +7457,7 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B176" t="s">
         <v>167</v>
@@ -7488,7 +7489,7 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B177" t="s">
         <v>168</v>
@@ -7517,7 +7518,7 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B178" t="s">
         <v>171</v>
@@ -7549,7 +7550,7 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B179" t="s">
         <v>171</v>
@@ -7581,7 +7582,7 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B180" t="s">
         <v>172</v>
@@ -7613,7 +7614,7 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B181" t="s">
         <v>174</v>
@@ -7645,7 +7646,7 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B182" t="s">
         <v>175</v>
@@ -7677,7 +7678,7 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B183" t="s">
         <v>177</v>
@@ -7709,7 +7710,7 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B184" t="s">
         <v>60</v>
@@ -7741,7 +7742,7 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B185" t="s">
         <v>60</v>
@@ -7773,7 +7774,7 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B186" t="s">
         <v>60</v>
@@ -7805,7 +7806,7 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B187" t="s">
         <v>181</v>
@@ -7837,7 +7838,7 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B188" t="s">
         <v>182</v>
@@ -7869,7 +7870,7 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B189" t="s">
         <v>182</v>
@@ -7901,7 +7902,7 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B190" t="s">
         <v>182</v>
@@ -7933,7 +7934,7 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B191" t="s">
         <v>183</v>
@@ -7965,7 +7966,7 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B192" t="s">
         <v>184</v>
@@ -7994,7 +7995,7 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B193" t="s">
         <v>185</v>
@@ -8023,10 +8024,10 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B194" t="s">
-        <v>186</v>
+        <v>24</v>
       </c>
       <c r="C194" t="s">
         <v>11</v>
@@ -8035,13 +8036,13 @@
         <v>25</v>
       </c>
       <c r="E194">
-        <v>2500</v>
+        <v>3167</v>
       </c>
       <c r="F194" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G194" s="2">
-        <v>46229</v>
+        <v>46291</v>
       </c>
       <c r="H194" t="s">
         <v>156</v>
@@ -8055,10 +8056,10 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B195" t="s">
-        <v>186</v>
+        <v>24</v>
       </c>
       <c r="C195" t="s">
         <v>11</v>
@@ -8067,16 +8068,16 @@
         <v>25</v>
       </c>
       <c r="E195">
-        <v>2500</v>
+        <v>3167</v>
       </c>
       <c r="F195" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G195" s="2">
-        <v>46229</v>
+        <v>46291</v>
       </c>
       <c r="H195" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="I195" t="s">
         <v>14</v>
@@ -8087,10 +8088,10 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B196" t="s">
-        <v>186</v>
+        <v>24</v>
       </c>
       <c r="C196" t="s">
         <v>11</v>
@@ -8099,13 +8100,13 @@
         <v>26</v>
       </c>
       <c r="E196">
-        <v>3500</v>
+        <v>2833</v>
       </c>
       <c r="F196" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G196" s="2">
-        <v>46229</v>
+        <v>46291</v>
       </c>
       <c r="H196" t="s">
         <v>156</v>
@@ -8119,10 +8120,10 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B197" t="s">
-        <v>186</v>
+        <v>24</v>
       </c>
       <c r="C197" t="s">
         <v>11</v>
@@ -8131,16 +8132,16 @@
         <v>26</v>
       </c>
       <c r="E197">
-        <v>3500</v>
+        <v>2833</v>
       </c>
       <c r="F197" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G197" s="2">
-        <v>46229</v>
+        <v>46291</v>
       </c>
       <c r="H197" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="I197" t="s">
         <v>14</v>
@@ -8151,45 +8152,45 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B198" t="s">
-        <v>24</v>
+        <v>187</v>
       </c>
       <c r="C198" t="s">
         <v>11</v>
       </c>
       <c r="D198" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E198">
-        <v>3167</v>
+        <v>47600</v>
       </c>
       <c r="F198" s="1">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="G198" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H198" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="I198" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J198" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B199" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="C199" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D199" t="s">
         <v>25</v>
@@ -8197,14 +8198,11 @@
       <c r="E199">
         <v>3167</v>
       </c>
-      <c r="F199" s="1">
-        <v>46281</v>
-      </c>
       <c r="G199" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H199" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="I199" t="s">
         <v>14</v>
@@ -8215,28 +8213,25 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B200" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="C200" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D200" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E200">
-        <v>2833</v>
-      </c>
-      <c r="F200" s="1">
-        <v>46281</v>
+        <v>3167</v>
       </c>
       <c r="G200" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H200" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="I200" t="s">
         <v>14</v>
@@ -8247,13 +8242,13 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B201" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="C201" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D201" t="s">
         <v>26</v>
@@ -8261,14 +8256,11 @@
       <c r="E201">
         <v>2833</v>
       </c>
-      <c r="F201" s="1">
-        <v>46281</v>
-      </c>
       <c r="G201" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H201" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="I201" t="s">
         <v>14</v>
@@ -8279,34 +8271,31 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B202" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="C202" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D202" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E202">
-        <v>47600</v>
-      </c>
-      <c r="F202" s="1">
-        <v>46295</v>
+        <v>2833</v>
       </c>
       <c r="G202" s="2">
         <v>46321</v>
       </c>
       <c r="H202" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I202" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J202" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.35">
@@ -8314,22 +8303,25 @@
         <v>356</v>
       </c>
       <c r="B203" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="C203" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D203" t="s">
         <v>25</v>
       </c>
       <c r="E203">
-        <v>3167</v>
+        <v>2000</v>
+      </c>
+      <c r="F203" s="1">
+        <v>46295</v>
       </c>
       <c r="G203" s="2">
-        <v>46321</v>
+        <v>46260</v>
       </c>
       <c r="H203" t="s">
-        <v>156</v>
+        <v>22</v>
       </c>
       <c r="I203" t="s">
         <v>14</v>
@@ -8343,22 +8335,25 @@
         <v>356</v>
       </c>
       <c r="B204" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="C204" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D204" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E204">
-        <v>3167</v>
+        <v>6000</v>
+      </c>
+      <c r="F204" s="1">
+        <v>46295</v>
       </c>
       <c r="G204" s="2">
-        <v>46321</v>
+        <v>46260</v>
       </c>
       <c r="H204" t="s">
-        <v>187</v>
+        <v>22</v>
       </c>
       <c r="I204" t="s">
         <v>14</v>
@@ -8372,57 +8367,63 @@
         <v>356</v>
       </c>
       <c r="B205" t="s">
-        <v>126</v>
+        <v>189</v>
       </c>
       <c r="C205" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D205" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="E205">
-        <v>2833</v>
+        <v>29483</v>
+      </c>
+      <c r="F205" s="1">
+        <v>46281</v>
       </c>
       <c r="G205" s="2">
-        <v>46321</v>
+        <v>46291</v>
       </c>
       <c r="H205" t="s">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="I205" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="J205" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B206" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="C206" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D206" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E206">
-        <v>2833</v>
+        <v>286171</v>
+      </c>
+      <c r="F206" s="1">
+        <v>46265</v>
       </c>
       <c r="G206" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H206" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="I206" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J206" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.35">
@@ -8430,31 +8431,31 @@
         <v>357</v>
       </c>
       <c r="B207" t="s">
-        <v>24</v>
+        <v>193</v>
       </c>
       <c r="C207" t="s">
         <v>11</v>
       </c>
       <c r="D207" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E207">
-        <v>2000</v>
+        <v>36000</v>
       </c>
       <c r="F207" s="1">
-        <v>46295</v>
+        <v>46281</v>
       </c>
       <c r="G207" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H207" t="s">
-        <v>22</v>
+        <v>194</v>
       </c>
       <c r="I207" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J207" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.35">
@@ -8462,63 +8463,63 @@
         <v>357</v>
       </c>
       <c r="B208" t="s">
-        <v>24</v>
+        <v>193</v>
       </c>
       <c r="C208" t="s">
         <v>11</v>
       </c>
       <c r="D208" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E208">
-        <v>6000</v>
+        <v>23998.54</v>
       </c>
       <c r="F208" s="1">
-        <v>46295</v>
+        <v>46281</v>
       </c>
       <c r="G208" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H208" t="s">
-        <v>22</v>
+        <v>192</v>
       </c>
       <c r="I208" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J208" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B209" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C209" t="s">
         <v>11</v>
       </c>
       <c r="D209" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="E209">
-        <v>29483</v>
+        <v>1575</v>
       </c>
       <c r="F209" s="1">
-        <v>46281</v>
+        <v>46265</v>
       </c>
       <c r="G209" s="2">
-        <v>46291</v>
+        <v>46229</v>
       </c>
       <c r="H209" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="I209" t="s">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="J209" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.35">
@@ -8526,16 +8527,16 @@
         <v>358</v>
       </c>
       <c r="B210" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C210" t="s">
         <v>11</v>
       </c>
       <c r="D210" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E210">
-        <v>286171</v>
+        <v>2925</v>
       </c>
       <c r="F210" s="1">
         <v>46265</v>
@@ -8544,13 +8545,13 @@
         <v>46229</v>
       </c>
       <c r="H210" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I210" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J210" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.35">
@@ -8558,31 +8559,31 @@
         <v>358</v>
       </c>
       <c r="B211" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C211" t="s">
         <v>11</v>
       </c>
       <c r="D211" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E211">
-        <v>36000</v>
+        <v>1575</v>
       </c>
       <c r="F211" s="1">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="G211" s="2">
-        <v>46291</v>
+        <v>46229</v>
       </c>
       <c r="H211" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I211" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J211" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.35">
@@ -8590,31 +8591,31 @@
         <v>358</v>
       </c>
       <c r="B212" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C212" t="s">
         <v>11</v>
       </c>
       <c r="D212" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E212">
-        <v>23998.54</v>
+        <v>2925</v>
       </c>
       <c r="F212" s="1">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="G212" s="2">
-        <v>46291</v>
+        <v>46229</v>
       </c>
       <c r="H212" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I212" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J212" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.35">
@@ -8622,16 +8623,16 @@
         <v>359</v>
       </c>
       <c r="B213" t="s">
-        <v>196</v>
+        <v>126</v>
       </c>
       <c r="C213" t="s">
         <v>11</v>
       </c>
       <c r="D213" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E213">
-        <v>1575</v>
+        <v>3328.15</v>
       </c>
       <c r="F213" s="1">
         <v>46265</v>
@@ -8640,7 +8641,7 @@
         <v>46229</v>
       </c>
       <c r="H213" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I213" t="s">
         <v>14</v>
@@ -8654,16 +8655,16 @@
         <v>359</v>
       </c>
       <c r="B214" t="s">
-        <v>196</v>
+        <v>126</v>
       </c>
       <c r="C214" t="s">
         <v>11</v>
       </c>
       <c r="D214" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E214">
-        <v>2925</v>
+        <v>6180.85</v>
       </c>
       <c r="F214" s="1">
         <v>46265</v>
@@ -8672,7 +8673,7 @@
         <v>46229</v>
       </c>
       <c r="H214" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I214" t="s">
         <v>14</v>
@@ -8686,25 +8687,25 @@
         <v>359</v>
       </c>
       <c r="B215" t="s">
+        <v>126</v>
+      </c>
+      <c r="C215" t="s">
+        <v>11</v>
+      </c>
+      <c r="D215" t="s">
+        <v>25</v>
+      </c>
+      <c r="E215">
+        <v>3328.15</v>
+      </c>
+      <c r="F215" s="1">
+        <v>46265</v>
+      </c>
+      <c r="G215" s="2">
+        <v>46260</v>
+      </c>
+      <c r="H215" t="s">
         <v>199</v>
-      </c>
-      <c r="C215" t="s">
-        <v>11</v>
-      </c>
-      <c r="D215" t="s">
-        <v>26</v>
-      </c>
-      <c r="E215">
-        <v>1575</v>
-      </c>
-      <c r="F215" s="1">
-        <v>46295</v>
-      </c>
-      <c r="G215" s="2">
-        <v>46229</v>
-      </c>
-      <c r="H215" t="s">
-        <v>197</v>
       </c>
       <c r="I215" t="s">
         <v>14</v>
@@ -8718,25 +8719,25 @@
         <v>359</v>
       </c>
       <c r="B216" t="s">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="C216" t="s">
         <v>11</v>
       </c>
       <c r="D216" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E216">
-        <v>2925</v>
+        <v>6180.85</v>
       </c>
       <c r="F216" s="1">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="G216" s="2">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="H216" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I216" t="s">
         <v>14</v>
@@ -8747,135 +8748,135 @@
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B217" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="C217" t="s">
         <v>11</v>
       </c>
       <c r="D217" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E217">
-        <v>3328.15</v>
+        <v>5250</v>
       </c>
       <c r="F217" s="1">
         <v>46265</v>
       </c>
       <c r="G217" s="2">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="H217" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I217" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="J217" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B218" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="C218" t="s">
         <v>11</v>
       </c>
       <c r="D218" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E218">
-        <v>6180.85</v>
+        <v>9750</v>
       </c>
       <c r="F218" s="1">
         <v>46265</v>
       </c>
       <c r="G218" s="2">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="H218" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I218" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="J218" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B219" t="s">
-        <v>126</v>
+        <v>203</v>
       </c>
       <c r="C219" t="s">
         <v>11</v>
       </c>
       <c r="D219" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E219">
-        <v>3328.15</v>
+        <v>17000</v>
       </c>
       <c r="F219" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G219" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H219" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="I219" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J219" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B220" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="C220" t="s">
         <v>11</v>
       </c>
       <c r="D220" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E220">
-        <v>6180.85</v>
+        <v>5250</v>
       </c>
       <c r="F220" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G220" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H220" t="s">
         <v>201</v>
       </c>
       <c r="I220" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="J220" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B221" t="s">
         <v>47</v>
@@ -8887,13 +8888,13 @@
         <v>47</v>
       </c>
       <c r="E221">
-        <v>5250</v>
+        <v>9750</v>
       </c>
       <c r="F221" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G221" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H221" t="s">
         <v>202</v>
@@ -8907,124 +8908,115 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B222" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C222" t="s">
         <v>11</v>
       </c>
       <c r="D222" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="E222">
-        <v>9750</v>
+        <v>9509</v>
       </c>
       <c r="F222" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G222" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H222" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I222" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="J222" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B223" t="s">
-        <v>204</v>
+        <v>126</v>
       </c>
       <c r="C223" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D223" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E223">
-        <v>17000</v>
-      </c>
-      <c r="F223" s="1">
-        <v>46281</v>
+        <v>3328.15</v>
       </c>
       <c r="G223" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H223" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I223" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J223" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B224" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="C224" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D224" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="E224">
-        <v>5250</v>
-      </c>
-      <c r="F224" s="1">
-        <v>46281</v>
+        <v>6180.85</v>
       </c>
       <c r="G224" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H224" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I224" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="J224" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B225" t="s">
         <v>47</v>
       </c>
       <c r="C225" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D225" t="s">
         <v>47</v>
       </c>
       <c r="E225">
-        <v>9750</v>
-      </c>
-      <c r="F225" s="1">
-        <v>46281</v>
+        <v>15000</v>
       </c>
       <c r="G225" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H225" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I225" t="s">
         <v>49</v>
@@ -9038,7 +9030,7 @@
         <v>360</v>
       </c>
       <c r="B226" t="s">
-        <v>24</v>
+        <v>206</v>
       </c>
       <c r="C226" t="s">
         <v>11</v>
@@ -9047,7 +9039,7 @@
         <v>25</v>
       </c>
       <c r="E226">
-        <v>9509</v>
+        <v>675023456</v>
       </c>
       <c r="F226" s="1">
         <v>46281</v>
@@ -9056,7 +9048,7 @@
         <v>46291</v>
       </c>
       <c r="H226" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I226" t="s">
         <v>14</v>
@@ -9070,22 +9062,25 @@
         <v>360</v>
       </c>
       <c r="B227" t="s">
-        <v>126</v>
+        <v>206</v>
       </c>
       <c r="C227" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D227" t="s">
         <v>25</v>
       </c>
       <c r="E227">
-        <v>3328.15</v>
+        <v>6750</v>
+      </c>
+      <c r="F227" s="1">
+        <v>46281</v>
       </c>
       <c r="G227" s="2">
-        <v>46321</v>
+        <v>46291</v>
       </c>
       <c r="H227" t="s">
-        <v>200</v>
+        <v>157</v>
       </c>
       <c r="I227" t="s">
         <v>14</v>
@@ -9096,54 +9091,60 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B228" t="s">
-        <v>126</v>
+        <v>208</v>
       </c>
       <c r="C228" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D228" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E228">
-        <v>6180.85</v>
+        <v>6000</v>
+      </c>
+      <c r="F228" s="1">
+        <v>46265</v>
       </c>
       <c r="G228" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H228" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="I228" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="J228" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B229" t="s">
-        <v>47</v>
+        <v>208</v>
       </c>
       <c r="C229" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D229" t="s">
         <v>47</v>
       </c>
       <c r="E229">
-        <v>15000</v>
+        <v>6000</v>
+      </c>
+      <c r="F229" s="1">
+        <v>46265</v>
       </c>
       <c r="G229" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H229" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="I229" t="s">
         <v>49</v>
@@ -9157,7 +9158,7 @@
         <v>361</v>
       </c>
       <c r="B230" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C230" t="s">
         <v>11</v>
@@ -9166,16 +9167,16 @@
         <v>25</v>
       </c>
       <c r="E230">
-        <v>6750</v>
+        <v>4590</v>
       </c>
       <c r="F230" s="1">
-        <v>46281</v>
+        <v>46265</v>
       </c>
       <c r="G230" s="2">
-        <v>46291</v>
+        <v>46229</v>
       </c>
       <c r="H230" t="s">
-        <v>208</v>
+        <v>156</v>
       </c>
       <c r="I230" t="s">
         <v>14</v>
@@ -9189,7 +9190,7 @@
         <v>361</v>
       </c>
       <c r="B231" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C231" t="s">
         <v>11</v>
@@ -9198,13 +9199,13 @@
         <v>25</v>
       </c>
       <c r="E231">
-        <v>6750</v>
+        <v>4590</v>
       </c>
       <c r="F231" s="1">
-        <v>46281</v>
+        <v>46265</v>
       </c>
       <c r="G231" s="2">
-        <v>46291</v>
+        <v>46229</v>
       </c>
       <c r="H231" t="s">
         <v>157</v>
@@ -9218,19 +9219,19 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B232" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C232" t="s">
         <v>11</v>
       </c>
       <c r="D232" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="E232">
-        <v>6000</v>
+        <v>33600</v>
       </c>
       <c r="F232" s="1">
         <v>46265</v>
@@ -9239,53 +9240,53 @@
         <v>46229</v>
       </c>
       <c r="H232" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="I232" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J232" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B233" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C233" t="s">
         <v>11</v>
       </c>
       <c r="D233" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="E233">
-        <v>6000</v>
+        <v>3385</v>
       </c>
       <c r="F233" s="1">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="G233" s="2">
-        <v>46229</v>
+        <v>46321</v>
       </c>
       <c r="H233" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="I233" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="J233" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B234" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C234" t="s">
         <v>11</v>
@@ -9294,16 +9295,16 @@
         <v>25</v>
       </c>
       <c r="E234">
-        <v>4590</v>
+        <v>3385</v>
       </c>
       <c r="F234" s="1">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="G234" s="2">
-        <v>46229</v>
+        <v>46321</v>
       </c>
       <c r="H234" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I234" t="s">
         <v>14</v>
@@ -9314,39 +9315,39 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B235" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C235" t="s">
         <v>11</v>
       </c>
       <c r="D235" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E235">
-        <v>4590</v>
+        <v>55600</v>
       </c>
       <c r="F235" s="1">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="G235" s="2">
-        <v>46229</v>
+        <v>46321</v>
       </c>
       <c r="H235" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="I235" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J235" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B236" t="s">
         <v>213</v>
@@ -9355,42 +9356,42 @@
         <v>11</v>
       </c>
       <c r="D236" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E236">
-        <v>33600</v>
+        <v>8750</v>
       </c>
       <c r="F236" s="1">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="G236" s="2">
-        <v>46229</v>
+        <v>46321</v>
       </c>
       <c r="H236" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="I236" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="J236" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B237" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C237" t="s">
         <v>11</v>
       </c>
       <c r="D237" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E237">
-        <v>3385</v>
+        <v>8750</v>
       </c>
       <c r="F237" s="1">
         <v>46295</v>
@@ -9399,13 +9400,13 @@
         <v>46321</v>
       </c>
       <c r="H237" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="I237" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="J237" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.35">
@@ -9413,7 +9414,7 @@
         <v>362</v>
       </c>
       <c r="B238" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C238" t="s">
         <v>11</v>
@@ -9422,16 +9423,16 @@
         <v>25</v>
       </c>
       <c r="E238">
-        <v>3385</v>
+        <v>4500</v>
       </c>
       <c r="F238" s="1">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="G238" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H238" t="s">
-        <v>157</v>
+        <v>22</v>
       </c>
       <c r="I238" t="s">
         <v>14</v>
@@ -9445,31 +9446,31 @@
         <v>362</v>
       </c>
       <c r="B239" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C239" t="s">
         <v>11</v>
       </c>
       <c r="D239" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E239">
-        <v>55600</v>
+        <v>4500</v>
       </c>
       <c r="F239" s="1">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="G239" s="2">
-        <v>46321</v>
+        <v>46260</v>
       </c>
       <c r="H239" t="s">
-        <v>215</v>
+        <v>22</v>
       </c>
       <c r="I239" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J239" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.35">
@@ -9477,31 +9478,28 @@
         <v>362</v>
       </c>
       <c r="B240" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C240" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D240" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="E240">
-        <v>8750</v>
-      </c>
-      <c r="F240" s="1">
-        <v>46295</v>
+        <v>4000</v>
       </c>
       <c r="G240" s="2">
         <v>46321</v>
       </c>
       <c r="H240" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="I240" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="J240" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.35">
@@ -9509,31 +9507,28 @@
         <v>362</v>
       </c>
       <c r="B241" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C241" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D241" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="E241">
-        <v>8750</v>
-      </c>
-      <c r="F241" s="1">
-        <v>46295</v>
+        <v>4500</v>
       </c>
       <c r="G241" s="2">
         <v>46321</v>
       </c>
       <c r="H241" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I241" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="J241" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.35">
@@ -9541,31 +9536,31 @@
         <v>363</v>
       </c>
       <c r="B242" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C242" t="s">
         <v>11</v>
       </c>
       <c r="D242" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E242">
-        <v>4500</v>
+        <v>42534.54</v>
       </c>
       <c r="F242" s="1">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="G242" s="2">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="H242" t="s">
-        <v>22</v>
+        <v>178</v>
       </c>
       <c r="I242" t="s">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="J242" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.35">
@@ -9573,89 +9568,95 @@
         <v>363</v>
       </c>
       <c r="B243" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C243" t="s">
         <v>11</v>
       </c>
       <c r="D243" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E243">
-        <v>4500</v>
+        <v>2621836</v>
       </c>
       <c r="F243" s="1">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="G243" s="2">
         <v>46260</v>
       </c>
       <c r="H243" t="s">
-        <v>22</v>
+        <v>224</v>
       </c>
       <c r="I243" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J243" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B244" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C244" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D244" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E244">
-        <v>4000</v>
+        <v>6300</v>
+      </c>
+      <c r="F244" s="1">
+        <v>46265</v>
       </c>
       <c r="G244" s="2">
-        <v>46321</v>
+        <v>46260</v>
       </c>
       <c r="H244" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="I244" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J244" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B245" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C245" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D245" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E245">
-        <v>4500</v>
+        <v>11700</v>
+      </c>
+      <c r="F245" s="1">
+        <v>46265</v>
       </c>
       <c r="G245" s="2">
-        <v>46321</v>
+        <v>46260</v>
       </c>
       <c r="H245" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="I245" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J245" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.35">
@@ -9663,31 +9664,31 @@
         <v>364</v>
       </c>
       <c r="B246" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C246" t="s">
         <v>11</v>
       </c>
       <c r="D246" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="E246">
-        <v>42534.54</v>
+        <v>3000</v>
       </c>
       <c r="F246" s="1">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="G246" s="2">
         <v>46260</v>
       </c>
       <c r="H246" t="s">
-        <v>178</v>
+        <v>229</v>
       </c>
       <c r="I246" t="s">
-        <v>179</v>
+        <v>230</v>
       </c>
       <c r="J246" t="s">
-        <v>180</v>
+        <v>231</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.35">
@@ -9695,39 +9696,39 @@
         <v>364</v>
       </c>
       <c r="B247" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C247" t="s">
         <v>11</v>
       </c>
       <c r="D247" t="s">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="E247">
-        <v>2621836</v>
+        <v>3000</v>
       </c>
       <c r="F247" s="1">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="G247" s="2">
         <v>46260</v>
       </c>
       <c r="H247" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="I247" t="s">
-        <v>31</v>
+        <v>230</v>
       </c>
       <c r="J247" t="s">
-        <v>32</v>
+        <v>231</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B248" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C248" t="s">
         <v>11</v>
@@ -9736,7 +9737,7 @@
         <v>17</v>
       </c>
       <c r="E248">
-        <v>6300</v>
+        <v>6000</v>
       </c>
       <c r="F248" s="1">
         <v>46265</v>
@@ -9745,7 +9746,7 @@
         <v>46260</v>
       </c>
       <c r="H248" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="I248" t="s">
         <v>19</v>
@@ -9756,10 +9757,10 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B249" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C249" t="s">
         <v>11</v>
@@ -9768,7 +9769,7 @@
         <v>17</v>
       </c>
       <c r="E249">
-        <v>11700</v>
+        <v>6000</v>
       </c>
       <c r="F249" s="1">
         <v>46265</v>
@@ -9777,7 +9778,7 @@
         <v>46260</v>
       </c>
       <c r="H249" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="I249" t="s">
         <v>19</v>
@@ -9788,10 +9789,10 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B250" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C250" t="s">
         <v>11</v>
@@ -9800,7 +9801,7 @@
         <v>100</v>
       </c>
       <c r="E250">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="F250" s="1">
         <v>46265</v>
@@ -9809,21 +9810,21 @@
         <v>46260</v>
       </c>
       <c r="H250" t="s">
+        <v>229</v>
+      </c>
+      <c r="I250" t="s">
         <v>230</v>
       </c>
-      <c r="I250" t="s">
+      <c r="J250" t="s">
         <v>231</v>
-      </c>
-      <c r="J250" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B251" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C251" t="s">
         <v>11</v>
@@ -9832,7 +9833,7 @@
         <v>100</v>
       </c>
       <c r="E251">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="F251" s="1">
         <v>46265</v>
@@ -9841,21 +9842,21 @@
         <v>46260</v>
       </c>
       <c r="H251" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I251" t="s">
+        <v>230</v>
+      </c>
+      <c r="J251" t="s">
         <v>231</v>
-      </c>
-      <c r="J251" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B252" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C252" t="s">
         <v>11</v>
@@ -9864,7 +9865,7 @@
         <v>17</v>
       </c>
       <c r="E252">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="F252" s="1">
         <v>46265</v>
@@ -9873,7 +9874,7 @@
         <v>46260</v>
       </c>
       <c r="H252" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I252" t="s">
         <v>19</v>
@@ -9884,10 +9885,10 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B253" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C253" t="s">
         <v>11</v>
@@ -9896,7 +9897,7 @@
         <v>17</v>
       </c>
       <c r="E253">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="F253" s="1">
         <v>46265</v>
@@ -9905,7 +9906,7 @@
         <v>46260</v>
       </c>
       <c r="H253" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I253" t="s">
         <v>19</v>
@@ -9916,7 +9917,7 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B254" t="s">
         <v>236</v>
@@ -9937,18 +9938,18 @@
         <v>46260</v>
       </c>
       <c r="H254" t="s">
+        <v>229</v>
+      </c>
+      <c r="I254" t="s">
         <v>230</v>
       </c>
-      <c r="I254" t="s">
+      <c r="J254" t="s">
         <v>231</v>
-      </c>
-      <c r="J254" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B255" t="s">
         <v>236</v>
@@ -9969,18 +9970,18 @@
         <v>46260</v>
       </c>
       <c r="H255" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I255" t="s">
+        <v>230</v>
+      </c>
+      <c r="J255" t="s">
         <v>231</v>
-      </c>
-      <c r="J255" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B256" t="s">
         <v>236</v>
@@ -9992,7 +9993,7 @@
         <v>17</v>
       </c>
       <c r="E256">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="F256" s="1">
         <v>46265</v>
@@ -10001,7 +10002,7 @@
         <v>46260</v>
       </c>
       <c r="H256" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I256" t="s">
         <v>19</v>
@@ -10012,7 +10013,7 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B257" t="s">
         <v>236</v>
@@ -10024,7 +10025,7 @@
         <v>17</v>
       </c>
       <c r="E257">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="F257" s="1">
         <v>46265</v>
@@ -10033,7 +10034,7 @@
         <v>46260</v>
       </c>
       <c r="H257" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I257" t="s">
         <v>19</v>
@@ -10044,7 +10045,7 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B258" t="s">
         <v>237</v>
@@ -10053,65 +10054,65 @@
         <v>11</v>
       </c>
       <c r="D258" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E258">
-        <v>1000</v>
+        <v>12000</v>
       </c>
       <c r="F258" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G258" s="2">
         <v>46260</v>
       </c>
       <c r="H258" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="I258" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="J258" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B259" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C259" t="s">
         <v>11</v>
       </c>
       <c r="D259" t="s">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="E259">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F259" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G259" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H259" t="s">
         <v>233</v>
       </c>
       <c r="I259" t="s">
-        <v>231</v>
+        <v>19</v>
       </c>
       <c r="J259" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B260" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C260" t="s">
         <v>11</v>
@@ -10120,13 +10121,13 @@
         <v>17</v>
       </c>
       <c r="E260">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="F260" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G260" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H260" t="s">
         <v>234</v>
@@ -10140,74 +10141,74 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B261" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C261" t="s">
         <v>11</v>
       </c>
       <c r="D261" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="E261">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="F261" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G261" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H261" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="I261" t="s">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="J261" t="s">
-        <v>20</v>
+        <v>231</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B262" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C262" t="s">
         <v>11</v>
       </c>
       <c r="D262" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E262">
-        <v>12000</v>
+        <v>1000</v>
       </c>
       <c r="F262" s="1">
         <v>46281</v>
       </c>
       <c r="G262" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H262" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="I262" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="J262" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B263" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C263" t="s">
         <v>11</v>
@@ -10216,7 +10217,7 @@
         <v>17</v>
       </c>
       <c r="E263">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="F263" s="1">
         <v>46281</v>
@@ -10225,7 +10226,7 @@
         <v>46291</v>
       </c>
       <c r="H263" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="I263" t="s">
         <v>19</v>
@@ -10236,10 +10237,10 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B264" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C264" t="s">
         <v>11</v>
@@ -10248,7 +10249,7 @@
         <v>17</v>
       </c>
       <c r="E264">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="F264" s="1">
         <v>46281</v>
@@ -10257,7 +10258,7 @@
         <v>46291</v>
       </c>
       <c r="H264" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I264" t="s">
         <v>19</v>
@@ -10268,10 +10269,10 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B265" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="C265" t="s">
         <v>11</v>
@@ -10280,7 +10281,7 @@
         <v>100</v>
       </c>
       <c r="E265">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="F265" s="1">
         <v>46281</v>
@@ -10289,30 +10290,30 @@
         <v>46291</v>
       </c>
       <c r="H265" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I265" t="s">
+        <v>230</v>
+      </c>
+      <c r="J265" t="s">
         <v>231</v>
-      </c>
-      <c r="J265" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B266" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="C266" t="s">
         <v>11</v>
       </c>
       <c r="D266" t="s">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="E266">
-        <v>1000</v>
+        <v>16000</v>
       </c>
       <c r="F266" s="1">
         <v>46281</v>
@@ -10321,30 +10322,30 @@
         <v>46291</v>
       </c>
       <c r="H266" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="I266" t="s">
-        <v>231</v>
+        <v>19</v>
       </c>
       <c r="J266" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B267" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C267" t="s">
         <v>11</v>
       </c>
       <c r="D267" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="E267">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="F267" s="1">
         <v>46281</v>
@@ -10353,21 +10354,21 @@
         <v>46291</v>
       </c>
       <c r="H267" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="I267" t="s">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="J267" t="s">
-        <v>20</v>
+        <v>231</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B268" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C268" t="s">
         <v>11</v>
@@ -10376,7 +10377,7 @@
         <v>17</v>
       </c>
       <c r="E268">
-        <v>4000</v>
+        <v>18000</v>
       </c>
       <c r="F268" s="1">
         <v>46281</v>
@@ -10385,7 +10386,7 @@
         <v>46291</v>
       </c>
       <c r="H268" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="I268" t="s">
         <v>19</v>
@@ -10396,7 +10397,7 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B269" t="s">
         <v>236</v>
@@ -10408,7 +10409,7 @@
         <v>100</v>
       </c>
       <c r="E269">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="F269" s="1">
         <v>46281</v>
@@ -10417,18 +10418,18 @@
         <v>46291</v>
       </c>
       <c r="H269" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="I269" t="s">
+        <v>230</v>
+      </c>
+      <c r="J269" t="s">
         <v>231</v>
-      </c>
-      <c r="J269" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B270" t="s">
         <v>236</v>
@@ -10437,10 +10438,10 @@
         <v>11</v>
       </c>
       <c r="D270" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="E270">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="F270" s="1">
         <v>46281</v>
@@ -10449,30 +10450,30 @@
         <v>46291</v>
       </c>
       <c r="H270" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="I270" t="s">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="J270" t="s">
-        <v>20</v>
+        <v>231</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B271" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="C271" t="s">
         <v>11</v>
       </c>
       <c r="D271" t="s">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="E271">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="F271" s="1">
         <v>46281</v>
@@ -10481,21 +10482,21 @@
         <v>46291</v>
       </c>
       <c r="H271" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="I271" t="s">
-        <v>231</v>
+        <v>19</v>
       </c>
       <c r="J271" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B272" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="C272" t="s">
         <v>11</v>
@@ -10504,7 +10505,7 @@
         <v>17</v>
       </c>
       <c r="E272">
-        <v>18000</v>
+        <v>6000</v>
       </c>
       <c r="F272" s="1">
         <v>46281</v>
@@ -10513,7 +10514,7 @@
         <v>46291</v>
       </c>
       <c r="H272" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="I272" t="s">
         <v>19</v>
@@ -10524,16 +10525,16 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B273" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C273" t="s">
         <v>11</v>
       </c>
       <c r="D273" t="s">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="E273">
         <v>2000</v>
@@ -10545,27 +10546,27 @@
         <v>46291</v>
       </c>
       <c r="H273" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="I273" t="s">
-        <v>231</v>
+        <v>19</v>
       </c>
       <c r="J273" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B274" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C274" t="s">
         <v>11</v>
       </c>
       <c r="D274" t="s">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="E274">
         <v>2000</v>
@@ -10577,30 +10578,30 @@
         <v>46291</v>
       </c>
       <c r="H274" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I274" t="s">
-        <v>231</v>
+        <v>19</v>
       </c>
       <c r="J274" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B275" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C275" t="s">
         <v>11</v>
       </c>
       <c r="D275" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="E275">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="F275" s="1">
         <v>46281</v>
@@ -10609,30 +10610,30 @@
         <v>46291</v>
       </c>
       <c r="H275" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="I275" t="s">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="J275" t="s">
-        <v>20</v>
+        <v>231</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B276" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C276" t="s">
         <v>11</v>
       </c>
       <c r="D276" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="E276">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="F276" s="1">
         <v>46281</v>
@@ -10641,21 +10642,21 @@
         <v>46291</v>
       </c>
       <c r="H276" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I276" t="s">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="J276" t="s">
-        <v>20</v>
+        <v>231</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B277" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C277" t="s">
         <v>11</v>
@@ -10664,7 +10665,7 @@
         <v>17</v>
       </c>
       <c r="E277">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="F277" s="1">
         <v>46281</v>
@@ -10673,7 +10674,7 @@
         <v>46291</v>
       </c>
       <c r="H277" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I277" t="s">
         <v>19</v>
@@ -10684,28 +10685,25 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B278" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="C278" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D278" t="s">
         <v>17</v>
       </c>
       <c r="E278">
-        <v>2000</v>
-      </c>
-      <c r="F278" s="1">
-        <v>46281</v>
+        <v>219776</v>
       </c>
       <c r="G278" s="2">
         <v>46291</v>
       </c>
       <c r="H278" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="I278" t="s">
         <v>19</v>
@@ -10716,135 +10714,126 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B279" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C279" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D279" t="s">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="E279">
-        <v>2000</v>
-      </c>
-      <c r="F279" s="1">
-        <v>46281</v>
+        <v>164834</v>
       </c>
       <c r="G279" s="2">
         <v>46291</v>
       </c>
       <c r="H279" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="I279" t="s">
-        <v>231</v>
+        <v>19</v>
       </c>
       <c r="J279" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B280" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C280" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D280" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E280">
-        <v>2000</v>
-      </c>
-      <c r="F280" s="1">
-        <v>46281</v>
+        <v>71955</v>
       </c>
       <c r="G280" s="2">
         <v>46291</v>
       </c>
       <c r="H280" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="I280" t="s">
-        <v>231</v>
+        <v>19</v>
       </c>
       <c r="J280" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B281" t="s">
+        <v>235</v>
+      </c>
+      <c r="C281" t="s">
+        <v>28</v>
+      </c>
+      <c r="D281" t="s">
+        <v>100</v>
+      </c>
+      <c r="E281">
+        <v>5000</v>
+      </c>
+      <c r="G281" s="2">
+        <v>46321</v>
+      </c>
+      <c r="H281" t="s">
         <v>242</v>
       </c>
-      <c r="C281" t="s">
-        <v>11</v>
-      </c>
-      <c r="D281" t="s">
-        <v>17</v>
-      </c>
-      <c r="E281">
-        <v>12000</v>
-      </c>
-      <c r="F281" s="1">
-        <v>46281</v>
-      </c>
-      <c r="G281" s="2">
-        <v>46291</v>
-      </c>
-      <c r="H281" t="s">
-        <v>246</v>
-      </c>
       <c r="I281" t="s">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="J281" t="s">
-        <v>20</v>
+        <v>231</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B282" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C282" t="s">
         <v>28</v>
       </c>
       <c r="D282" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="E282">
-        <v>219776</v>
+        <v>5000</v>
       </c>
       <c r="G282" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H282" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="I282" t="s">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="J282" t="s">
-        <v>20</v>
+        <v>231</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B283" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C283" t="s">
         <v>28</v>
@@ -10853,13 +10842,13 @@
         <v>17</v>
       </c>
       <c r="E283">
-        <v>164834</v>
+        <v>12000</v>
       </c>
       <c r="G283" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H283" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="I283" t="s">
         <v>19</v>
@@ -10870,25 +10859,25 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B284" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C284" t="s">
         <v>28</v>
       </c>
       <c r="D284" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="E284">
-        <v>71955</v>
+        <v>12000</v>
       </c>
       <c r="G284" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H284" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="I284" t="s">
         <v>19</v>
@@ -10902,28 +10891,31 @@
         <v>365</v>
       </c>
       <c r="B285" t="s">
-        <v>236</v>
+        <v>94</v>
       </c>
       <c r="C285" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D285" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E285">
-        <v>5000</v>
+        <v>1450</v>
+      </c>
+      <c r="F285" s="1">
+        <v>46265</v>
       </c>
       <c r="G285" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H285" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="I285" t="s">
-        <v>231</v>
+        <v>14</v>
       </c>
       <c r="J285" t="s">
-        <v>232</v>
+        <v>15</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.35">
@@ -10931,28 +10923,31 @@
         <v>365</v>
       </c>
       <c r="B286" t="s">
-        <v>236</v>
+        <v>94</v>
       </c>
       <c r="C286" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D286" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E286">
-        <v>5000</v>
+        <v>1450</v>
+      </c>
+      <c r="F286" s="1">
+        <v>46265</v>
       </c>
       <c r="G286" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H286" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="I286" t="s">
-        <v>231</v>
+        <v>14</v>
       </c>
       <c r="J286" t="s">
-        <v>232</v>
+        <v>15</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.35">
@@ -10960,28 +10955,31 @@
         <v>365</v>
       </c>
       <c r="B287" t="s">
-        <v>236</v>
+        <v>94</v>
       </c>
       <c r="C287" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D287" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E287">
-        <v>12000</v>
+        <v>800</v>
+      </c>
+      <c r="F287" s="1">
+        <v>46265</v>
       </c>
       <c r="G287" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H287" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="I287" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J287" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.35">
@@ -10989,36 +10987,39 @@
         <v>365</v>
       </c>
       <c r="B288" t="s">
-        <v>236</v>
+        <v>94</v>
       </c>
       <c r="C288" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D288" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E288">
-        <v>12000</v>
+        <v>800</v>
+      </c>
+      <c r="F288" s="1">
+        <v>46265</v>
       </c>
       <c r="G288" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H288" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="I288" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J288" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B289" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C289" t="s">
         <v>11</v>
@@ -11027,16 +11028,16 @@
         <v>25</v>
       </c>
       <c r="E289">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="F289" s="1">
         <v>46265</v>
       </c>
       <c r="G289" s="2">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="H289" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I289" t="s">
         <v>14</v>
@@ -11047,10 +11048,10 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B290" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C290" t="s">
         <v>11</v>
@@ -11059,16 +11060,16 @@
         <v>25</v>
       </c>
       <c r="E290">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="F290" s="1">
         <v>46265</v>
       </c>
       <c r="G290" s="2">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="H290" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I290" t="s">
         <v>14</v>
@@ -11079,10 +11080,10 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B291" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C291" t="s">
         <v>11</v>
@@ -11091,16 +11092,16 @@
         <v>26</v>
       </c>
       <c r="E291">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="F291" s="1">
         <v>46265</v>
       </c>
       <c r="G291" s="2">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="H291" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I291" t="s">
         <v>14</v>
@@ -11111,10 +11112,10 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B292" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C292" t="s">
         <v>11</v>
@@ -11123,16 +11124,16 @@
         <v>26</v>
       </c>
       <c r="E292">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="F292" s="1">
         <v>46265</v>
       </c>
       <c r="G292" s="2">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="H292" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I292" t="s">
         <v>14</v>
@@ -11143,19 +11144,19 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B293" t="s">
-        <v>98</v>
+        <v>252</v>
       </c>
       <c r="C293" t="s">
         <v>11</v>
       </c>
       <c r="D293" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E293">
-        <v>1500</v>
+        <v>36000</v>
       </c>
       <c r="F293" s="1">
         <v>46265</v>
@@ -11164,21 +11165,21 @@
         <v>46260</v>
       </c>
       <c r="H293" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I293" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J293" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B294" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C294" t="s">
         <v>11</v>
@@ -11190,13 +11191,13 @@
         <v>1500</v>
       </c>
       <c r="F294" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G294" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H294" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I294" t="s">
         <v>14</v>
@@ -11207,25 +11208,25 @@
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B295" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C295" t="s">
         <v>11</v>
       </c>
       <c r="D295" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E295">
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="F295" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G295" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H295" t="s">
         <v>251</v>
@@ -11239,10 +11240,10 @@
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B296" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C296" t="s">
         <v>11</v>
@@ -11254,13 +11255,13 @@
         <v>750</v>
       </c>
       <c r="F296" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G296" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H296" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I296" t="s">
         <v>14</v>
@@ -11271,51 +11272,51 @@
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B297" t="s">
-        <v>253</v>
+        <v>107</v>
       </c>
       <c r="C297" t="s">
         <v>11</v>
       </c>
       <c r="D297" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E297">
-        <v>36000</v>
+        <v>750</v>
       </c>
       <c r="F297" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G297" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H297" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="I297" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J297" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B298" t="s">
-        <v>107</v>
+        <v>254</v>
       </c>
       <c r="C298" t="s">
         <v>11</v>
       </c>
       <c r="D298" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E298">
-        <v>1500</v>
+        <v>14000</v>
       </c>
       <c r="F298" s="1">
         <v>46281</v>
@@ -11324,30 +11325,30 @@
         <v>46291</v>
       </c>
       <c r="H298" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I298" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J298" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B299" t="s">
-        <v>107</v>
+        <v>256</v>
       </c>
       <c r="C299" t="s">
         <v>11</v>
       </c>
       <c r="D299" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="E299">
-        <v>1500</v>
+        <v>46400</v>
       </c>
       <c r="F299" s="1">
         <v>46281</v>
@@ -11356,30 +11357,30 @@
         <v>46291</v>
       </c>
       <c r="H299" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="I299" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
       <c r="J299" t="s">
-        <v>15</v>
+        <v>231</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B300" t="s">
-        <v>107</v>
+        <v>256</v>
       </c>
       <c r="C300" t="s">
         <v>11</v>
       </c>
       <c r="D300" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E300">
-        <v>750</v>
+        <v>18000</v>
       </c>
       <c r="F300" s="1">
         <v>46281</v>
@@ -11388,173 +11389,161 @@
         <v>46291</v>
       </c>
       <c r="H300" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I300" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J300" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B301" t="s">
-        <v>107</v>
+        <v>258</v>
       </c>
       <c r="C301" t="s">
         <v>11</v>
       </c>
       <c r="D301" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E301">
-        <v>750</v>
+        <v>36000</v>
       </c>
       <c r="F301" s="1">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="G301" s="2">
         <v>46291</v>
       </c>
       <c r="H301" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I301" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J301" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B302" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C302" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D302" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E302">
-        <v>14000</v>
-      </c>
-      <c r="F302" s="1">
-        <v>46281</v>
+        <v>1500</v>
       </c>
       <c r="G302" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H302" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="I302" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J302" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B303" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C303" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D303" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E303">
-        <v>46400</v>
-      </c>
-      <c r="F303" s="1">
-        <v>46281</v>
+        <v>1500</v>
       </c>
       <c r="G303" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H303" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="I303" t="s">
-        <v>231</v>
+        <v>14</v>
       </c>
       <c r="J303" t="s">
-        <v>232</v>
+        <v>15</v>
       </c>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B304" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C304" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D304" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E304">
-        <v>18000</v>
-      </c>
-      <c r="F304" s="1">
-        <v>46281</v>
+        <v>750</v>
       </c>
       <c r="G304" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H304" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I304" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J304" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B305" t="s">
         <v>259</v>
       </c>
       <c r="C305" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D305" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E305">
-        <v>36000</v>
-      </c>
-      <c r="F305" s="1">
-        <v>46295</v>
+        <v>750</v>
       </c>
       <c r="G305" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H305" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="I305" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J305" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.35">
@@ -11562,22 +11551,25 @@
         <v>366</v>
       </c>
       <c r="B306" t="s">
-        <v>260</v>
+        <v>60</v>
       </c>
       <c r="C306" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D306" t="s">
         <v>25</v>
       </c>
       <c r="E306">
-        <v>1500</v>
+        <v>1286.95</v>
+      </c>
+      <c r="F306" s="1">
+        <v>46265</v>
       </c>
       <c r="G306" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H306" t="s">
-        <v>251</v>
+        <v>147</v>
       </c>
       <c r="I306" t="s">
         <v>14</v>
@@ -11591,22 +11583,25 @@
         <v>366</v>
       </c>
       <c r="B307" t="s">
-        <v>260</v>
+        <v>60</v>
       </c>
       <c r="C307" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D307" t="s">
         <v>25</v>
       </c>
       <c r="E307">
-        <v>1500</v>
+        <v>2390.0500000000002</v>
+      </c>
+      <c r="F307" s="1">
+        <v>46265</v>
       </c>
       <c r="G307" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H307" t="s">
-        <v>252</v>
+        <v>148</v>
       </c>
       <c r="I307" t="s">
         <v>14</v>
@@ -11620,22 +11615,25 @@
         <v>366</v>
       </c>
       <c r="B308" t="s">
-        <v>260</v>
+        <v>60</v>
       </c>
       <c r="C308" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D308" t="s">
         <v>26</v>
       </c>
       <c r="E308">
-        <v>750</v>
+        <v>1163.05</v>
+      </c>
+      <c r="F308" s="1">
+        <v>46265</v>
       </c>
       <c r="G308" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H308" t="s">
-        <v>251</v>
+        <v>147</v>
       </c>
       <c r="I308" t="s">
         <v>14</v>
@@ -11649,22 +11647,25 @@
         <v>366</v>
       </c>
       <c r="B309" t="s">
-        <v>260</v>
+        <v>60</v>
       </c>
       <c r="C309" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D309" t="s">
         <v>26</v>
       </c>
       <c r="E309">
-        <v>750</v>
+        <v>2159.9499999999998</v>
+      </c>
+      <c r="F309" s="1">
+        <v>46265</v>
       </c>
       <c r="G309" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H309" t="s">
-        <v>252</v>
+        <v>148</v>
       </c>
       <c r="I309" t="s">
         <v>14</v>
@@ -11675,10 +11676,10 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B310" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="C310" t="s">
         <v>11</v>
@@ -11687,10 +11688,10 @@
         <v>25</v>
       </c>
       <c r="E310">
-        <v>1286.95</v>
+        <v>1111.95</v>
       </c>
       <c r="F310" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G310" s="2">
         <v>46229</v>
@@ -11707,10 +11708,10 @@
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B311" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="C311" t="s">
         <v>11</v>
@@ -11719,10 +11720,10 @@
         <v>25</v>
       </c>
       <c r="E311">
-        <v>2390.0500000000002</v>
+        <v>2065.0500000000002</v>
       </c>
       <c r="F311" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G311" s="2">
         <v>46229</v>
@@ -11739,10 +11740,10 @@
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B312" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="C312" t="s">
         <v>11</v>
@@ -11751,10 +11752,10 @@
         <v>26</v>
       </c>
       <c r="E312">
-        <v>1163.05</v>
+        <v>1338.05</v>
       </c>
       <c r="F312" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G312" s="2">
         <v>46229</v>
@@ -11771,10 +11772,10 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B313" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="C313" t="s">
         <v>11</v>
@@ -11783,10 +11784,10 @@
         <v>26</v>
       </c>
       <c r="E313">
-        <v>2159.9499999999998</v>
+        <v>2484.9499999999998</v>
       </c>
       <c r="F313" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G313" s="2">
         <v>46229</v>
@@ -11806,31 +11807,31 @@
         <v>367</v>
       </c>
       <c r="B314" t="s">
-        <v>122</v>
+        <v>260</v>
       </c>
       <c r="C314" t="s">
         <v>11</v>
       </c>
       <c r="D314" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E314">
-        <v>1111.95</v>
+        <v>1453363</v>
       </c>
       <c r="F314" s="1">
         <v>46281</v>
       </c>
       <c r="G314" s="2">
-        <v>46229</v>
+        <v>46291</v>
       </c>
       <c r="H314" t="s">
-        <v>147</v>
+        <v>261</v>
       </c>
       <c r="I314" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J314" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.35">
@@ -11838,31 +11839,28 @@
         <v>367</v>
       </c>
       <c r="B315" t="s">
-        <v>122</v>
+        <v>262</v>
       </c>
       <c r="C315" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D315" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E315">
-        <v>2065.0500000000002</v>
-      </c>
-      <c r="F315" s="1">
-        <v>46281</v>
+        <v>111112</v>
       </c>
       <c r="G315" s="2">
-        <v>46229</v>
+        <v>46321</v>
       </c>
       <c r="H315" t="s">
-        <v>148</v>
+        <v>263</v>
       </c>
       <c r="I315" t="s">
-        <v>14</v>
+        <v>264</v>
       </c>
       <c r="J315" t="s">
-        <v>15</v>
+        <v>265</v>
       </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.35">
@@ -11870,31 +11868,28 @@
         <v>367</v>
       </c>
       <c r="B316" t="s">
-        <v>122</v>
+        <v>262</v>
       </c>
       <c r="C316" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D316" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E316">
-        <v>1338.05</v>
-      </c>
-      <c r="F316" s="1">
-        <v>46281</v>
+        <v>221881.25</v>
       </c>
       <c r="G316" s="2">
-        <v>46229</v>
+        <v>46321</v>
       </c>
       <c r="H316" t="s">
-        <v>147</v>
+        <v>266</v>
       </c>
       <c r="I316" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J316" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.35">
@@ -11902,31 +11897,28 @@
         <v>367</v>
       </c>
       <c r="B317" t="s">
-        <v>122</v>
+        <v>262</v>
       </c>
       <c r="C317" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D317" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="E317">
-        <v>2484.9499999999998</v>
-      </c>
-      <c r="F317" s="1">
-        <v>46281</v>
+        <v>46766.75</v>
       </c>
       <c r="G317" s="2">
-        <v>46229</v>
+        <v>46321</v>
       </c>
       <c r="H317" t="s">
-        <v>148</v>
+        <v>263</v>
       </c>
       <c r="I317" t="s">
-        <v>14</v>
+        <v>264</v>
       </c>
       <c r="J317" t="s">
-        <v>15</v>
+        <v>265</v>
       </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.35">
@@ -11934,31 +11926,31 @@
         <v>368</v>
       </c>
       <c r="B318" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C318" t="s">
         <v>11</v>
       </c>
       <c r="D318" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E318">
-        <v>1453363</v>
+        <v>6300</v>
       </c>
       <c r="F318" s="1">
-        <v>46281</v>
+        <v>46265</v>
       </c>
       <c r="G318" s="2">
-        <v>46291</v>
+        <v>46229</v>
       </c>
       <c r="H318" t="s">
-        <v>262</v>
+        <v>108</v>
       </c>
       <c r="I318" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="J318" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.35">
@@ -11966,28 +11958,31 @@
         <v>368</v>
       </c>
       <c r="B319" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C319" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D319" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="E319">
-        <v>111112</v>
+        <v>11700</v>
+      </c>
+      <c r="F319" s="1">
+        <v>46265</v>
       </c>
       <c r="G319" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H319" t="s">
-        <v>264</v>
+        <v>111</v>
       </c>
       <c r="I319" t="s">
-        <v>265</v>
+        <v>109</v>
       </c>
       <c r="J319" t="s">
-        <v>266</v>
+        <v>110</v>
       </c>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.35">
@@ -11995,28 +11990,31 @@
         <v>368</v>
       </c>
       <c r="B320" t="s">
-        <v>263</v>
+        <v>24</v>
       </c>
       <c r="C320" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D320" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E320">
-        <v>221881.25</v>
+        <v>700</v>
+      </c>
+      <c r="F320" s="1">
+        <v>46265</v>
       </c>
       <c r="G320" s="2">
-        <v>46321</v>
+        <v>46260</v>
       </c>
       <c r="H320" t="s">
-        <v>267</v>
+        <v>124</v>
       </c>
       <c r="I320" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J320" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.35">
@@ -12024,97 +12022,100 @@
         <v>368</v>
       </c>
       <c r="B321" t="s">
-        <v>263</v>
+        <v>24</v>
       </c>
       <c r="C321" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D321" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="E321">
-        <v>46766.75</v>
+        <v>1300</v>
+      </c>
+      <c r="F321" s="1">
+        <v>46265</v>
       </c>
       <c r="G321" s="2">
-        <v>46321</v>
+        <v>46260</v>
       </c>
       <c r="H321" t="s">
-        <v>264</v>
+        <v>125</v>
       </c>
       <c r="I321" t="s">
-        <v>265</v>
+        <v>14</v>
       </c>
       <c r="J321" t="s">
-        <v>266</v>
+        <v>15</v>
       </c>
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B322" t="s">
+        <v>24</v>
+      </c>
+      <c r="C322" t="s">
+        <v>11</v>
+      </c>
+      <c r="D322" t="s">
+        <v>26</v>
+      </c>
+      <c r="E322">
+        <v>1750</v>
+      </c>
+      <c r="F322" s="1">
+        <v>46265</v>
+      </c>
+      <c r="G322" s="2">
+        <v>46260</v>
+      </c>
+      <c r="H322" t="s">
         <v>268</v>
       </c>
-      <c r="C322" t="s">
-        <v>11</v>
-      </c>
-      <c r="D322" t="s">
-        <v>17</v>
-      </c>
-      <c r="E322">
-        <v>6300</v>
-      </c>
-      <c r="F322" s="1">
-        <v>46265</v>
-      </c>
-      <c r="G322" s="2">
-        <v>46229</v>
-      </c>
-      <c r="H322" t="s">
-        <v>108</v>
-      </c>
       <c r="I322" t="s">
-        <v>109</v>
+        <v>14</v>
       </c>
       <c r="J322" t="s">
-        <v>110</v>
+        <v>15</v>
       </c>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B323" t="s">
-        <v>268</v>
+        <v>24</v>
       </c>
       <c r="C323" t="s">
         <v>11</v>
       </c>
       <c r="D323" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E323">
-        <v>11700</v>
+        <v>3250</v>
       </c>
       <c r="F323" s="1">
         <v>46265</v>
       </c>
       <c r="G323" s="2">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="H323" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="I323" t="s">
-        <v>109</v>
+        <v>14</v>
       </c>
       <c r="J323" t="s">
-        <v>110</v>
+        <v>15</v>
       </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B324" t="s">
         <v>24</v>
@@ -12123,10 +12124,10 @@
         <v>11</v>
       </c>
       <c r="D324" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E324">
-        <v>700</v>
+        <v>875</v>
       </c>
       <c r="F324" s="1">
         <v>46265</v>
@@ -12135,7 +12136,7 @@
         <v>46260</v>
       </c>
       <c r="H324" t="s">
-        <v>124</v>
+        <v>268</v>
       </c>
       <c r="I324" t="s">
         <v>14</v>
@@ -12146,7 +12147,7 @@
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B325" t="s">
         <v>24</v>
@@ -12155,10 +12156,10 @@
         <v>11</v>
       </c>
       <c r="D325" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E325">
-        <v>1300</v>
+        <v>1625</v>
       </c>
       <c r="F325" s="1">
         <v>46265</v>
@@ -12178,92 +12179,92 @@
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B326" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="C326" t="s">
         <v>11</v>
       </c>
       <c r="D326" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="E326">
-        <v>1750</v>
+        <v>2992.5</v>
       </c>
       <c r="F326" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G326" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H326" t="s">
         <v>269</v>
       </c>
       <c r="I326" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="J326" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B327" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="C327" t="s">
         <v>11</v>
       </c>
       <c r="D327" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="E327">
-        <v>3250</v>
+        <v>5557.5</v>
       </c>
       <c r="F327" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G327" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H327" t="s">
-        <v>125</v>
+        <v>270</v>
       </c>
       <c r="I327" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="J327" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B328" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C328" t="s">
         <v>11</v>
       </c>
       <c r="D328" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="E328">
-        <v>875</v>
+        <v>7800</v>
       </c>
       <c r="F328" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G328" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H328" t="s">
-        <v>269</v>
+        <v>125</v>
       </c>
       <c r="I328" t="s">
         <v>14</v>
@@ -12274,51 +12275,51 @@
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B329" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C329" t="s">
         <v>11</v>
       </c>
       <c r="D329" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="E329">
-        <v>1625</v>
+        <v>4200</v>
       </c>
       <c r="F329" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G329" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H329" t="s">
-        <v>125</v>
+        <v>271</v>
       </c>
       <c r="I329" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="J329" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B330" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="C330" t="s">
         <v>11</v>
       </c>
       <c r="D330" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="E330">
-        <v>2992.5</v>
+        <v>5850</v>
       </c>
       <c r="F330" s="1">
         <v>46281</v>
@@ -12327,30 +12328,30 @@
         <v>46291</v>
       </c>
       <c r="H330" t="s">
-        <v>270</v>
+        <v>125</v>
       </c>
       <c r="I330" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="J330" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B331" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="C331" t="s">
         <v>11</v>
       </c>
       <c r="D331" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="E331">
-        <v>5557.5</v>
+        <v>3150</v>
       </c>
       <c r="F331" s="1">
         <v>46281</v>
@@ -12362,36 +12363,36 @@
         <v>271</v>
       </c>
       <c r="I331" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="J331" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B332" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C332" t="s">
         <v>11</v>
       </c>
       <c r="D332" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="E332">
-        <v>7800</v>
+        <v>700</v>
       </c>
       <c r="F332" s="1">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="G332" s="2">
         <v>46291</v>
       </c>
       <c r="H332" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I332" t="s">
         <v>14</v>
@@ -12402,60 +12403,60 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B333" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C333" t="s">
         <v>11</v>
       </c>
       <c r="D333" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="E333">
-        <v>4200</v>
+        <v>1300</v>
       </c>
       <c r="F333" s="1">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="G333" s="2">
         <v>46291</v>
       </c>
       <c r="H333" t="s">
-        <v>272</v>
+        <v>125</v>
       </c>
       <c r="I333" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="J333" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B334" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C334" t="s">
         <v>11</v>
       </c>
       <c r="D334" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="E334">
-        <v>5850</v>
+        <v>1750</v>
       </c>
       <c r="F334" s="1">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="G334" s="2">
         <v>46291</v>
       </c>
       <c r="H334" t="s">
-        <v>125</v>
+        <v>268</v>
       </c>
       <c r="I334" t="s">
         <v>14</v>
@@ -12466,60 +12467,57 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B335" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C335" t="s">
         <v>11</v>
       </c>
       <c r="D335" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="E335">
-        <v>3150</v>
+        <v>3250</v>
       </c>
       <c r="F335" s="1">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="G335" s="2">
         <v>46291</v>
       </c>
       <c r="H335" t="s">
-        <v>272</v>
+        <v>125</v>
       </c>
       <c r="I335" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="J335" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B336" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C336" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D336" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E336">
-        <v>700</v>
-      </c>
-      <c r="F336" s="1">
-        <v>46295</v>
+        <v>7800</v>
       </c>
       <c r="G336" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H336" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I336" t="s">
         <v>14</v>
@@ -12530,60 +12528,54 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B337" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C337" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D337" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E337">
-        <v>1300</v>
-      </c>
-      <c r="F337" s="1">
-        <v>46295</v>
+        <v>4200</v>
       </c>
       <c r="G337" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H337" t="s">
-        <v>125</v>
+        <v>271</v>
       </c>
       <c r="I337" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="J337" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B338" t="s">
         <v>24</v>
       </c>
       <c r="C338" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D338" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E338">
-        <v>1750</v>
-      </c>
-      <c r="F338" s="1">
-        <v>46295</v>
+        <v>700</v>
       </c>
       <c r="G338" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H338" t="s">
-        <v>269</v>
+        <v>124</v>
       </c>
       <c r="I338" t="s">
         <v>14</v>
@@ -12594,25 +12586,22 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B339" t="s">
         <v>24</v>
       </c>
       <c r="C339" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D339" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E339">
-        <v>3250</v>
-      </c>
-      <c r="F339" s="1">
-        <v>46295</v>
+        <v>1300</v>
       </c>
       <c r="G339" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H339" t="s">
         <v>125</v>
@@ -12626,25 +12615,25 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B340" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C340" t="s">
         <v>39</v>
       </c>
       <c r="D340" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="E340">
-        <v>7800</v>
+        <v>1750</v>
       </c>
       <c r="G340" s="2">
         <v>46321</v>
       </c>
       <c r="H340" t="s">
-        <v>125</v>
+        <v>268</v>
       </c>
       <c r="I340" t="s">
         <v>14</v>
@@ -12655,60 +12644,60 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B341" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C341" t="s">
         <v>39</v>
       </c>
       <c r="D341" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="E341">
-        <v>4200</v>
+        <v>3250</v>
       </c>
       <c r="G341" s="2">
         <v>46321</v>
       </c>
       <c r="H341" t="s">
-        <v>272</v>
+        <v>125</v>
       </c>
       <c r="I341" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="J341" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B342" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C342" t="s">
         <v>39</v>
       </c>
       <c r="D342" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E342">
-        <v>700</v>
+        <v>25532</v>
       </c>
       <c r="G342" s="2">
         <v>46321</v>
       </c>
       <c r="H342" t="s">
-        <v>124</v>
+        <v>272</v>
       </c>
       <c r="I342" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J342" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.35">
@@ -12716,22 +12705,25 @@
         <v>369</v>
       </c>
       <c r="B343" t="s">
-        <v>24</v>
+        <v>273</v>
       </c>
       <c r="C343" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D343" t="s">
         <v>25</v>
       </c>
       <c r="E343">
-        <v>1300</v>
+        <v>1879</v>
+      </c>
+      <c r="F343" s="1">
+        <v>46265</v>
       </c>
       <c r="G343" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H343" t="s">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="I343" t="s">
         <v>14</v>
@@ -12745,22 +12737,25 @@
         <v>369</v>
       </c>
       <c r="B344" t="s">
-        <v>24</v>
+        <v>273</v>
       </c>
       <c r="C344" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D344" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E344">
-        <v>1750</v>
+        <v>1879</v>
+      </c>
+      <c r="F344" s="1">
+        <v>46265</v>
       </c>
       <c r="G344" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H344" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="I344" t="s">
         <v>14</v>
@@ -12774,22 +12769,25 @@
         <v>369</v>
       </c>
       <c r="B345" t="s">
-        <v>24</v>
+        <v>273</v>
       </c>
       <c r="C345" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D345" t="s">
         <v>26</v>
       </c>
       <c r="E345">
-        <v>3250</v>
+        <v>1050</v>
+      </c>
+      <c r="F345" s="1">
+        <v>46265</v>
       </c>
       <c r="G345" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H345" t="s">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="I345" t="s">
         <v>14</v>
@@ -12803,33 +12801,36 @@
         <v>369</v>
       </c>
       <c r="B346" t="s">
-        <v>29</v>
+        <v>273</v>
       </c>
       <c r="C346" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D346" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E346">
-        <v>25532</v>
+        <v>1050</v>
+      </c>
+      <c r="F346" s="1">
+        <v>46265</v>
       </c>
       <c r="G346" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H346" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="I346" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J346" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B347" t="s">
         <v>274</v>
@@ -12838,30 +12839,30 @@
         <v>11</v>
       </c>
       <c r="D347" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="E347">
-        <v>1879</v>
+        <v>25000</v>
       </c>
       <c r="F347" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G347" s="2">
-        <v>46229</v>
+        <v>46291</v>
       </c>
       <c r="H347" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I347" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J347" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B348" t="s">
         <v>274</v>
@@ -12870,51 +12871,48 @@
         <v>11</v>
       </c>
       <c r="D348" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E348">
-        <v>1879</v>
+        <v>36000</v>
       </c>
       <c r="F348" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G348" s="2">
-        <v>46229</v>
+        <v>46291</v>
       </c>
       <c r="H348" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I348" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J348" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B349" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C349" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D349" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E349">
-        <v>1050</v>
-      </c>
-      <c r="F349" s="1">
-        <v>46265</v>
+        <v>1879</v>
       </c>
       <c r="G349" s="2">
-        <v>46229</v>
+        <v>46291</v>
       </c>
       <c r="H349" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I349" t="s">
         <v>14</v>
@@ -12925,28 +12923,25 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B350" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C350" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D350" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E350">
-        <v>1050</v>
-      </c>
-      <c r="F350" s="1">
-        <v>46265</v>
+        <v>1879</v>
       </c>
       <c r="G350" s="2">
-        <v>46229</v>
+        <v>46291</v>
       </c>
       <c r="H350" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I350" t="s">
         <v>14</v>
@@ -12957,71 +12952,65 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B351" t="s">
         <v>275</v>
       </c>
       <c r="C351" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D351" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="E351">
-        <v>25000</v>
-      </c>
-      <c r="F351" s="1">
-        <v>46281</v>
+        <v>1050</v>
       </c>
       <c r="G351" s="2">
         <v>46291</v>
       </c>
       <c r="H351" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I351" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J351" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B352" t="s">
         <v>275</v>
       </c>
       <c r="C352" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D352" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E352">
-        <v>36000</v>
-      </c>
-      <c r="F352" s="1">
-        <v>46281</v>
+        <v>1050</v>
       </c>
       <c r="G352" s="2">
         <v>46291</v>
       </c>
       <c r="H352" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="I352" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J352" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B353" t="s">
         <v>276</v>
@@ -13039,7 +13028,7 @@
         <v>46291</v>
       </c>
       <c r="H353" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I353" t="s">
         <v>14</v>
@@ -13050,7 +13039,7 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B354" t="s">
         <v>276</v>
@@ -13068,7 +13057,7 @@
         <v>46291</v>
       </c>
       <c r="H354" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I354" t="s">
         <v>14</v>
@@ -13079,7 +13068,7 @@
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B355" t="s">
         <v>276</v>
@@ -13097,7 +13086,7 @@
         <v>46291</v>
       </c>
       <c r="H355" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I355" t="s">
         <v>14</v>
@@ -13108,7 +13097,7 @@
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B356" t="s">
         <v>276</v>
@@ -13126,7 +13115,7 @@
         <v>46291</v>
       </c>
       <c r="H356" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I356" t="s">
         <v>14</v>
@@ -13143,25 +13132,28 @@
         <v>277</v>
       </c>
       <c r="C357" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D357" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E357">
-        <v>1879</v>
+        <v>194106.5</v>
+      </c>
+      <c r="F357" s="1">
+        <v>46265</v>
       </c>
       <c r="G357" s="2">
-        <v>46291</v>
+        <v>46260</v>
       </c>
       <c r="H357" t="s">
-        <v>251</v>
+        <v>106</v>
       </c>
       <c r="I357" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J357" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.35">
@@ -13169,28 +13161,31 @@
         <v>370</v>
       </c>
       <c r="B358" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C358" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D358" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E358">
-        <v>1879</v>
+        <v>18000</v>
+      </c>
+      <c r="F358" s="1">
+        <v>46281</v>
       </c>
       <c r="G358" s="2">
         <v>46291</v>
       </c>
       <c r="H358" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="I358" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J358" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.35">
@@ -13198,22 +13193,25 @@
         <v>370</v>
       </c>
       <c r="B359" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C359" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D359" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E359">
-        <v>1050</v>
+        <v>10600</v>
+      </c>
+      <c r="F359" s="1">
+        <v>46281</v>
       </c>
       <c r="G359" s="2">
         <v>46291</v>
       </c>
       <c r="H359" t="s">
-        <v>251</v>
+        <v>196</v>
       </c>
       <c r="I359" t="s">
         <v>14</v>
@@ -13224,25 +13222,28 @@
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B360" t="s">
-        <v>277</v>
+        <v>15</v>
       </c>
       <c r="C360" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D360" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E360">
-        <v>1050</v>
+        <v>6998</v>
+      </c>
+      <c r="F360" s="1">
+        <v>46265</v>
       </c>
       <c r="G360" s="2">
-        <v>46291</v>
+        <v>46229</v>
       </c>
       <c r="H360" t="s">
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="I360" t="s">
         <v>14</v>
@@ -13256,16 +13257,16 @@
         <v>371</v>
       </c>
       <c r="B361" t="s">
-        <v>278</v>
+        <v>15</v>
       </c>
       <c r="C361" t="s">
         <v>11</v>
       </c>
       <c r="D361" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E361">
-        <v>194106.5</v>
+        <v>4603</v>
       </c>
       <c r="F361" s="1">
         <v>46265</v>
@@ -13274,13 +13275,13 @@
         <v>46260</v>
       </c>
       <c r="H361" t="s">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="I361" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J361" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.35">
@@ -13288,31 +13289,31 @@
         <v>371</v>
       </c>
       <c r="B362" t="s">
-        <v>279</v>
+        <v>15</v>
       </c>
       <c r="C362" t="s">
         <v>11</v>
       </c>
       <c r="D362" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E362">
-        <v>18000</v>
+        <v>1778</v>
       </c>
       <c r="F362" s="1">
-        <v>46281</v>
+        <v>46265</v>
       </c>
       <c r="G362" s="2">
-        <v>46291</v>
+        <v>46260</v>
       </c>
       <c r="H362" t="s">
-        <v>280</v>
+        <v>196</v>
       </c>
       <c r="I362" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J362" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.35">
@@ -13320,39 +13321,36 @@
         <v>371</v>
       </c>
       <c r="B363" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C363" t="s">
         <v>11</v>
       </c>
       <c r="D363" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E363">
-        <v>10600</v>
-      </c>
-      <c r="F363" s="1">
-        <v>46281</v>
+        <v>49932</v>
       </c>
       <c r="G363" s="2">
-        <v>46291</v>
+        <v>46260</v>
       </c>
       <c r="H363" t="s">
-        <v>197</v>
+        <v>279</v>
       </c>
       <c r="I363" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J363" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B364" t="s">
-        <v>15</v>
+        <v>283</v>
       </c>
       <c r="C364" t="s">
         <v>11</v>
@@ -13361,80 +13359,74 @@
         <v>25</v>
       </c>
       <c r="E364">
-        <v>6998</v>
+        <v>4603</v>
       </c>
       <c r="F364" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G364" s="2">
         <v>46229</v>
       </c>
       <c r="H364" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I364" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="J364" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B365" t="s">
-        <v>15</v>
+        <v>283</v>
       </c>
       <c r="C365" t="s">
         <v>11</v>
       </c>
       <c r="D365" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E365">
-        <v>4603</v>
+        <v>1763</v>
       </c>
       <c r="F365" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G365" s="2">
-        <v>46260</v>
+        <v>46229</v>
       </c>
       <c r="H365" t="s">
-        <v>197</v>
+        <v>284</v>
       </c>
       <c r="I365" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="J365" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>372</v>
-      </c>
-      <c r="B366" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="C366" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D366" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E366">
-        <v>1778</v>
-      </c>
-      <c r="F366" s="1">
-        <v>46265</v>
+        <v>4603</v>
       </c>
       <c r="G366" s="2">
-        <v>46260</v>
+        <v>46321</v>
       </c>
       <c r="H366" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I366" t="s">
         <v>14</v>
@@ -13445,31 +13437,28 @@
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>372</v>
-      </c>
-      <c r="B367" t="s">
-        <v>283</v>
+        <v>371</v>
       </c>
       <c r="C367" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D367" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E367">
-        <v>49932</v>
+        <v>1714</v>
       </c>
       <c r="G367" s="2">
-        <v>46260</v>
+        <v>46321</v>
       </c>
       <c r="H367" t="s">
-        <v>280</v>
+        <v>196</v>
       </c>
       <c r="I367" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J367" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.35">
@@ -13477,7 +13466,7 @@
         <v>372</v>
       </c>
       <c r="B368" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C368" t="s">
         <v>11</v>
@@ -13486,22 +13475,22 @@
         <v>25</v>
       </c>
       <c r="E368">
-        <v>4603</v>
+        <v>3863</v>
       </c>
       <c r="F368" s="1">
-        <v>46281</v>
+        <v>46265</v>
       </c>
       <c r="G368" s="2">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="H368" t="s">
-        <v>285</v>
+        <v>22</v>
       </c>
       <c r="I368" t="s">
-        <v>109</v>
+        <v>14</v>
       </c>
       <c r="J368" t="s">
-        <v>110</v>
+        <v>15</v>
       </c>
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.35">
@@ -13509,7 +13498,7 @@
         <v>372</v>
       </c>
       <c r="B369" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C369" t="s">
         <v>11</v>
@@ -13518,42 +13507,48 @@
         <v>26</v>
       </c>
       <c r="E369">
-        <v>1763</v>
+        <v>3000</v>
       </c>
       <c r="F369" s="1">
-        <v>46281</v>
+        <v>46265</v>
       </c>
       <c r="G369" s="2">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="H369" t="s">
-        <v>285</v>
+        <v>22</v>
       </c>
       <c r="I369" t="s">
-        <v>109</v>
+        <v>14</v>
       </c>
       <c r="J369" t="s">
-        <v>110</v>
+        <v>15</v>
       </c>
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>372</v>
       </c>
+      <c r="B370" t="s">
+        <v>286</v>
+      </c>
       <c r="C370" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D370" t="s">
         <v>25</v>
       </c>
       <c r="E370">
-        <v>4603</v>
+        <v>3863</v>
+      </c>
+      <c r="F370" s="1">
+        <v>46295</v>
       </c>
       <c r="G370" s="2">
-        <v>46321</v>
+        <v>46291</v>
       </c>
       <c r="H370" t="s">
-        <v>197</v>
+        <v>22</v>
       </c>
       <c r="I370" t="s">
         <v>14</v>
@@ -13566,20 +13561,26 @@
       <c r="A371" t="s">
         <v>372</v>
       </c>
+      <c r="B371" t="s">
+        <v>286</v>
+      </c>
       <c r="C371" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D371" t="s">
         <v>26</v>
       </c>
       <c r="E371">
-        <v>1714</v>
+        <v>3130</v>
+      </c>
+      <c r="F371" s="1">
+        <v>46295</v>
       </c>
       <c r="G371" s="2">
-        <v>46321</v>
+        <v>46291</v>
       </c>
       <c r="H371" t="s">
-        <v>197</v>
+        <v>22</v>
       </c>
       <c r="I371" t="s">
         <v>14</v>
@@ -13590,57 +13591,51 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B372" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C372" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D372" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E372">
-        <v>3863</v>
-      </c>
-      <c r="F372" s="1">
-        <v>46265</v>
+        <v>24000</v>
       </c>
       <c r="G372" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H372" t="s">
-        <v>22</v>
+        <v>288</v>
       </c>
       <c r="I372" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="J372" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>286</v>
+        <v>24</v>
       </c>
       <c r="C373" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D373" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E373">
-        <v>3000</v>
-      </c>
-      <c r="F373" s="1">
-        <v>46265</v>
+        <v>3863</v>
       </c>
       <c r="G373" s="2">
-        <v>46260</v>
+        <v>46321</v>
       </c>
       <c r="H373" t="s">
         <v>22</v>
@@ -13654,25 +13649,22 @@
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>287</v>
+        <v>24</v>
       </c>
       <c r="C374" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D374" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E374">
-        <v>3863</v>
-      </c>
-      <c r="F374" s="1">
-        <v>46295</v>
+        <v>3000</v>
       </c>
       <c r="G374" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H374" t="s">
         <v>22</v>
@@ -13689,25 +13681,25 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>287</v>
+        <v>60</v>
       </c>
       <c r="C375" t="s">
         <v>11</v>
       </c>
       <c r="D375" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E375">
-        <v>3130</v>
+        <v>4958</v>
       </c>
       <c r="F375" s="1">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="G375" s="2">
-        <v>46291</v>
+        <v>46229</v>
       </c>
       <c r="H375" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="I375" t="s">
         <v>14</v>
@@ -13721,28 +13713,31 @@
         <v>373</v>
       </c>
       <c r="B376" t="s">
-        <v>288</v>
+        <v>60</v>
       </c>
       <c r="C376" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D376" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="E376">
-        <v>24000</v>
+        <v>4958</v>
+      </c>
+      <c r="F376" s="1">
+        <v>46265</v>
       </c>
       <c r="G376" s="2">
-        <v>46291</v>
+        <v>46229</v>
       </c>
       <c r="H376" t="s">
-        <v>289</v>
+        <v>62</v>
       </c>
       <c r="I376" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="J376" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.35">
@@ -13750,28 +13745,31 @@
         <v>373</v>
       </c>
       <c r="B377" t="s">
-        <v>24</v>
+        <v>289</v>
       </c>
       <c r="C377" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D377" t="s">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="E377">
-        <v>3863</v>
+        <v>166456.98000000001</v>
+      </c>
+      <c r="F377" s="1">
+        <v>46265</v>
       </c>
       <c r="G377" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H377" t="s">
-        <v>22</v>
+        <v>290</v>
       </c>
       <c r="I377" t="s">
-        <v>14</v>
+        <v>291</v>
       </c>
       <c r="J377" t="s">
-        <v>15</v>
+        <v>292</v>
       </c>
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.35">
@@ -13779,36 +13777,39 @@
         <v>373</v>
       </c>
       <c r="B378" t="s">
-        <v>24</v>
+        <v>289</v>
       </c>
       <c r="C378" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D378" t="s">
-        <v>26</v>
+        <v>128</v>
       </c>
       <c r="E378">
-        <v>3000</v>
+        <v>166456.98000000001</v>
+      </c>
+      <c r="F378" s="1">
+        <v>46265</v>
       </c>
       <c r="G378" s="2">
-        <v>46321</v>
+        <v>46229</v>
       </c>
       <c r="H378" t="s">
-        <v>22</v>
+        <v>293</v>
       </c>
       <c r="I378" t="s">
-        <v>14</v>
+        <v>291</v>
       </c>
       <c r="J378" t="s">
-        <v>15</v>
+        <v>292</v>
       </c>
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B379" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="C379" t="s">
         <v>11</v>
@@ -13817,13 +13818,13 @@
         <v>12</v>
       </c>
       <c r="E379">
-        <v>4958</v>
+        <v>4813</v>
       </c>
       <c r="F379" s="1">
         <v>46265</v>
       </c>
       <c r="G379" s="2">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="H379" t="s">
         <v>61</v>
@@ -13837,10 +13838,10 @@
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B380" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="C380" t="s">
         <v>11</v>
@@ -13849,13 +13850,13 @@
         <v>12</v>
       </c>
       <c r="E380">
-        <v>4958</v>
+        <v>4813</v>
       </c>
       <c r="F380" s="1">
         <v>46265</v>
       </c>
       <c r="G380" s="2">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="H380" t="s">
         <v>62</v>
@@ -13869,10 +13870,10 @@
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B381" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C381" t="s">
         <v>11</v>
@@ -13881,30 +13882,30 @@
         <v>128</v>
       </c>
       <c r="E381">
-        <v>166456.98000000001</v>
+        <v>3350</v>
       </c>
       <c r="F381" s="1">
         <v>46265</v>
       </c>
       <c r="G381" s="2">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="H381" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="I381" t="s">
-        <v>292</v>
+        <v>130</v>
       </c>
       <c r="J381" t="s">
-        <v>293</v>
+        <v>128</v>
       </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B382" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C382" t="s">
         <v>11</v>
@@ -13913,30 +13914,30 @@
         <v>128</v>
       </c>
       <c r="E382">
-        <v>166456.98000000001</v>
+        <v>3350</v>
       </c>
       <c r="F382" s="1">
         <v>46265</v>
       </c>
       <c r="G382" s="2">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="H382" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I382" t="s">
-        <v>292</v>
+        <v>130</v>
       </c>
       <c r="J382" t="s">
-        <v>293</v>
+        <v>128</v>
       </c>
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B383" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C383" t="s">
         <v>11</v>
@@ -13945,13 +13946,13 @@
         <v>12</v>
       </c>
       <c r="E383">
-        <v>4813</v>
+        <v>4808</v>
       </c>
       <c r="F383" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G383" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H383" t="s">
         <v>61</v>
@@ -13965,10 +13966,10 @@
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B384" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C384" t="s">
         <v>11</v>
@@ -13977,13 +13978,13 @@
         <v>12</v>
       </c>
       <c r="E384">
-        <v>4813</v>
+        <v>4808</v>
       </c>
       <c r="F384" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G384" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H384" t="s">
         <v>62</v>
@@ -13997,10 +13998,10 @@
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B385" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C385" t="s">
         <v>11</v>
@@ -14009,30 +14010,30 @@
         <v>128</v>
       </c>
       <c r="E385">
-        <v>3350</v>
+        <v>64800</v>
       </c>
       <c r="F385" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G385" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H385" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I385" t="s">
-        <v>130</v>
+        <v>299</v>
       </c>
       <c r="J385" t="s">
-        <v>128</v>
+        <v>300</v>
       </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B386" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C386" t="s">
         <v>11</v>
@@ -14041,45 +14042,42 @@
         <v>128</v>
       </c>
       <c r="E386">
-        <v>3350</v>
+        <v>64800</v>
       </c>
       <c r="F386" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G386" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H386" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="I386" t="s">
-        <v>130</v>
+        <v>299</v>
       </c>
       <c r="J386" t="s">
-        <v>128</v>
+        <v>300</v>
       </c>
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B387" t="s">
         <v>123</v>
       </c>
       <c r="C387" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D387" t="s">
         <v>12</v>
       </c>
       <c r="E387">
-        <v>4808</v>
-      </c>
-      <c r="F387" s="1">
-        <v>46281</v>
+        <v>4963</v>
       </c>
       <c r="G387" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H387" t="s">
         <v>61</v>
@@ -14093,25 +14091,22 @@
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B388" t="s">
         <v>123</v>
       </c>
       <c r="C388" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D388" t="s">
         <v>12</v>
       </c>
       <c r="E388">
-        <v>4808</v>
-      </c>
-      <c r="F388" s="1">
-        <v>46281</v>
+        <v>4963</v>
       </c>
       <c r="G388" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H388" t="s">
         <v>62</v>
@@ -14125,66 +14120,60 @@
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B389" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C389" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D389" t="s">
         <v>128</v>
       </c>
       <c r="E389">
-        <v>64800</v>
-      </c>
-      <c r="F389" s="1">
-        <v>46281</v>
+        <v>2865</v>
       </c>
       <c r="G389" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H389" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="I389" t="s">
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="J389" t="s">
-        <v>301</v>
+        <v>128</v>
       </c>
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B390" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C390" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D390" t="s">
         <v>128</v>
       </c>
       <c r="E390">
-        <v>64800</v>
-      </c>
-      <c r="F390" s="1">
-        <v>46281</v>
+        <v>2865</v>
       </c>
       <c r="G390" s="2">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="H390" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="I390" t="s">
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="J390" t="s">
-        <v>301</v>
+        <v>128</v>
       </c>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.35">
@@ -14192,115 +14181,127 @@
         <v>374</v>
       </c>
       <c r="B391" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="C391" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D391" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E391">
-        <v>4963</v>
+        <v>50010</v>
+      </c>
+      <c r="F391" s="1">
+        <v>46265</v>
       </c>
       <c r="G391" s="2">
-        <v>46321</v>
+        <v>46260</v>
       </c>
       <c r="H391" t="s">
-        <v>61</v>
+        <v>305</v>
       </c>
       <c r="I391" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J391" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B392" t="s">
-        <v>123</v>
+        <v>306</v>
       </c>
       <c r="C392" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D392" t="s">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="E392">
-        <v>4963</v>
+        <v>5000</v>
+      </c>
+      <c r="F392" s="1">
+        <v>46265</v>
       </c>
       <c r="G392" s="2">
-        <v>46321</v>
+        <v>46260</v>
       </c>
       <c r="H392" t="s">
-        <v>62</v>
+        <v>307</v>
       </c>
       <c r="I392" t="s">
-        <v>14</v>
+        <v>130</v>
       </c>
       <c r="J392" t="s">
-        <v>15</v>
+        <v>128</v>
       </c>
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B393" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C393" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D393" t="s">
-        <v>128</v>
+        <v>25</v>
       </c>
       <c r="E393">
-        <v>2865</v>
+        <v>4500</v>
+      </c>
+      <c r="F393" s="1">
+        <v>46265</v>
       </c>
       <c r="G393" s="2">
-        <v>46321</v>
+        <v>46260</v>
       </c>
       <c r="H393" t="s">
-        <v>304</v>
+        <v>22</v>
       </c>
       <c r="I393" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="J393" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B394" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C394" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D394" t="s">
-        <v>128</v>
+        <v>25</v>
       </c>
       <c r="E394">
-        <v>2865</v>
+        <v>4500</v>
+      </c>
+      <c r="F394" s="1">
+        <v>46265</v>
       </c>
       <c r="G394" s="2">
-        <v>46321</v>
+        <v>46260</v>
       </c>
       <c r="H394" t="s">
-        <v>305</v>
+        <v>22</v>
       </c>
       <c r="I394" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="J394" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.35">
@@ -14308,63 +14309,57 @@
         <v>375</v>
       </c>
       <c r="B395" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="C395" t="s">
         <v>11</v>
       </c>
       <c r="D395" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E395">
-        <v>50010</v>
+        <v>4500</v>
       </c>
       <c r="F395" s="1">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="G395" s="2">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="H395" t="s">
-        <v>306</v>
+        <v>22</v>
       </c>
       <c r="I395" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J395" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>376</v>
-      </c>
-      <c r="B396" t="s">
-        <v>307</v>
+        <v>375</v>
       </c>
       <c r="C396" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D396" t="s">
-        <v>128</v>
+        <v>25</v>
       </c>
       <c r="E396">
-        <v>5000</v>
-      </c>
-      <c r="F396" s="1">
-        <v>46265</v>
+        <v>4500</v>
       </c>
       <c r="G396" s="2">
-        <v>46260</v>
+        <v>46321</v>
       </c>
       <c r="H396" t="s">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="I396" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="J396" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.35">
@@ -14372,31 +14367,31 @@
         <v>376</v>
       </c>
       <c r="B397" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C397" t="s">
         <v>11</v>
       </c>
       <c r="D397" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E397">
-        <v>4500</v>
+        <v>90208</v>
       </c>
       <c r="F397" s="1">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="G397" s="2">
-        <v>46260</v>
+        <v>46229</v>
       </c>
       <c r="H397" t="s">
-        <v>22</v>
+        <v>233</v>
       </c>
       <c r="I397" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J397" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.35">
@@ -14410,25 +14405,25 @@
         <v>11</v>
       </c>
       <c r="D398" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E398">
-        <v>4500</v>
+        <v>90208</v>
       </c>
       <c r="F398" s="1">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="G398" s="2">
-        <v>46260</v>
+        <v>46229</v>
       </c>
       <c r="H398" t="s">
-        <v>22</v>
+        <v>234</v>
       </c>
       <c r="I398" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J398" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.35">
@@ -14436,16 +14431,16 @@
         <v>376</v>
       </c>
       <c r="B399" t="s">
-        <v>219</v>
+        <v>311</v>
       </c>
       <c r="C399" t="s">
         <v>11</v>
       </c>
       <c r="D399" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E399">
-        <v>4500</v>
+        <v>22552</v>
       </c>
       <c r="F399" s="1">
         <v>46281</v>
@@ -14454,103 +14449,109 @@
         <v>46291</v>
       </c>
       <c r="H399" t="s">
-        <v>22</v>
+        <v>233</v>
       </c>
       <c r="I399" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J399" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>376</v>
       </c>
+      <c r="B400" t="s">
+        <v>311</v>
+      </c>
       <c r="C400" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D400" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E400">
-        <v>4500</v>
+        <v>22552</v>
+      </c>
+      <c r="F400" s="1">
+        <v>46281</v>
       </c>
       <c r="G400" s="2">
-        <v>46321</v>
+        <v>46291</v>
       </c>
       <c r="H400" t="s">
-        <v>22</v>
+        <v>234</v>
       </c>
       <c r="I400" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J400" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B401" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C401" t="s">
         <v>11</v>
       </c>
       <c r="D401" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="E401">
-        <v>90208</v>
+        <v>33157</v>
       </c>
       <c r="F401" s="1">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="G401" s="2">
-        <v>46229</v>
+        <v>46291</v>
       </c>
       <c r="H401" t="s">
-        <v>234</v>
+        <v>313</v>
       </c>
       <c r="I401" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="J401" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B402" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C402" t="s">
         <v>11</v>
       </c>
       <c r="D402" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="E402">
-        <v>90208</v>
+        <v>33157</v>
       </c>
       <c r="F402" s="1">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="G402" s="2">
-        <v>46229</v>
+        <v>46291</v>
       </c>
       <c r="H402" t="s">
-        <v>235</v>
+        <v>314</v>
       </c>
       <c r="I402" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="J402" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.35">
@@ -14558,25 +14559,22 @@
         <v>377</v>
       </c>
       <c r="B403" t="s">
-        <v>312</v>
+        <v>175</v>
       </c>
       <c r="C403" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D403" t="s">
         <v>17</v>
       </c>
       <c r="E403">
-        <v>22552</v>
-      </c>
-      <c r="F403" s="1">
-        <v>46281</v>
+        <v>36000</v>
       </c>
       <c r="G403" s="2">
         <v>46291</v>
       </c>
       <c r="H403" t="s">
-        <v>234</v>
+        <v>18</v>
       </c>
       <c r="I403" t="s">
         <v>19</v>
@@ -14587,10 +14585,10 @@
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B404" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C404" t="s">
         <v>11</v>
@@ -14599,16 +14597,16 @@
         <v>17</v>
       </c>
       <c r="E404">
-        <v>22552</v>
+        <v>18000</v>
       </c>
       <c r="F404" s="1">
-        <v>46281</v>
+        <v>46265</v>
       </c>
       <c r="G404" s="2">
-        <v>46291</v>
+        <v>46229</v>
       </c>
       <c r="H404" t="s">
-        <v>235</v>
+        <v>316</v>
       </c>
       <c r="I404" t="s">
         <v>19</v>
@@ -14619,112 +14617,112 @@
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B405" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C405" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D405" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="E405">
-        <v>33157</v>
-      </c>
-      <c r="F405" s="1">
-        <v>46295</v>
+        <v>36000</v>
       </c>
       <c r="G405" s="2">
         <v>46291</v>
       </c>
       <c r="H405" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="I405" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="J405" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B406" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C406" t="s">
         <v>11</v>
       </c>
       <c r="D406" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E406">
-        <v>33157</v>
+        <v>4500</v>
       </c>
       <c r="F406" s="1">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="G406" s="2">
-        <v>46291</v>
+        <v>46229</v>
       </c>
       <c r="H406" t="s">
-        <v>315</v>
+        <v>156</v>
       </c>
       <c r="I406" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="J406" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B407" t="s">
-        <v>175</v>
+        <v>319</v>
       </c>
       <c r="C407" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D407" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E407">
-        <v>36000</v>
+        <v>4500</v>
+      </c>
+      <c r="F407" s="1">
+        <v>46265</v>
       </c>
       <c r="G407" s="2">
-        <v>46291</v>
+        <v>46229</v>
       </c>
       <c r="H407" t="s">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="I407" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J407" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B408" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C408" t="s">
         <v>11</v>
       </c>
       <c r="D408" t="s">
-        <v>17</v>
+        <v>128</v>
       </c>
       <c r="E408">
-        <v>18000</v>
+        <v>2500</v>
       </c>
       <c r="F408" s="1">
         <v>46265</v>
@@ -14733,13 +14731,13 @@
         <v>46229</v>
       </c>
       <c r="H408" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="I408" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
       <c r="J408" t="s">
-        <v>20</v>
+        <v>128</v>
       </c>
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.35">
@@ -14747,159 +14745,35 @@
         <v>380</v>
       </c>
       <c r="B409" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C409" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D409" t="s">
-        <v>17</v>
+        <v>128</v>
       </c>
       <c r="E409">
-        <v>36000</v>
+        <v>2500</v>
+      </c>
+      <c r="F409" s="1">
+        <v>46265</v>
       </c>
       <c r="G409" s="2">
-        <v>46291</v>
+        <v>46229</v>
       </c>
       <c r="H409" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="I409" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
       <c r="J409" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A410" t="s">
-        <v>381</v>
-      </c>
-      <c r="B410" t="s">
-        <v>320</v>
-      </c>
-      <c r="C410" t="s">
-        <v>11</v>
-      </c>
-      <c r="D410" t="s">
-        <v>25</v>
-      </c>
-      <c r="E410">
-        <v>4500</v>
-      </c>
-      <c r="F410" s="1">
-        <v>46265</v>
-      </c>
-      <c r="G410" s="2">
-        <v>46229</v>
-      </c>
-      <c r="H410" t="s">
-        <v>156</v>
-      </c>
-      <c r="I410" t="s">
-        <v>14</v>
-      </c>
-      <c r="J410" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A411" t="s">
-        <v>381</v>
-      </c>
-      <c r="B411" t="s">
-        <v>320</v>
-      </c>
-      <c r="C411" t="s">
-        <v>11</v>
-      </c>
-      <c r="D411" t="s">
-        <v>25</v>
-      </c>
-      <c r="E411">
-        <v>4500</v>
-      </c>
-      <c r="F411" s="1">
-        <v>46265</v>
-      </c>
-      <c r="G411" s="2">
-        <v>46229</v>
-      </c>
-      <c r="H411" t="s">
-        <v>321</v>
-      </c>
-      <c r="I411" t="s">
-        <v>14</v>
-      </c>
-      <c r="J411" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A412" t="s">
-        <v>381</v>
-      </c>
-      <c r="B412" t="s">
-        <v>320</v>
-      </c>
-      <c r="C412" t="s">
-        <v>11</v>
-      </c>
-      <c r="D412" t="s">
         <v>128</v>
       </c>
-      <c r="E412">
-        <v>2500</v>
-      </c>
-      <c r="F412" s="1">
-        <v>46265</v>
-      </c>
-      <c r="G412" s="2">
-        <v>46229</v>
-      </c>
-      <c r="H412" t="s">
-        <v>322</v>
-      </c>
-      <c r="I412" t="s">
-        <v>130</v>
-      </c>
-      <c r="J412" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A413" t="s">
-        <v>381</v>
-      </c>
-      <c r="B413" t="s">
-        <v>320</v>
-      </c>
-      <c r="C413" t="s">
-        <v>11</v>
-      </c>
-      <c r="D413" t="s">
-        <v>128</v>
-      </c>
-      <c r="E413">
-        <v>2500</v>
-      </c>
-      <c r="F413" s="1">
-        <v>46265</v>
-      </c>
-      <c r="G413" s="2">
-        <v>46229</v>
-      </c>
-      <c r="H413" t="s">
-        <v>323</v>
-      </c>
-      <c r="I413" t="s">
-        <v>130</v>
-      </c>
-      <c r="J413" t="s">
-        <v>128</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J409" xr:uid="{4AE04198-225E-4952-AFA7-99BB4D284234}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Employee_Expenses.xlsx
+++ b/data/Employee_Expenses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aneeba.hamid_karanda\Downloads\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B04E037-0483-4D8A-B79C-639A1A7CDE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C6194C-B337-498E-BE18-6207B9238811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E91F72FA-45AE-41E4-B25B-09DB7C520744}"/>
   </bookViews>
@@ -9039,7 +9039,7 @@
         <v>25</v>
       </c>
       <c r="E226">
-        <v>675023456</v>
+        <v>6750</v>
       </c>
       <c r="F226" s="1">
         <v>46281</v>
